--- a/results/Int Task Remove ACC 0.5/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-4.4286979627938816e-05 +/- 0.0007528786536758349</t>
+          <t>0.0056687333923826745 +/- 0.0014391564932924618</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.0028343666961912705 +/- 0.0011916407481907566</t>
+          <t>-0.001771479185119529 +/- 0.002335062236751828</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.000841452612931759 +/- 0.0009793332323957307</t>
+          <t>-0.0024800708591673935 +/- 0.0012400354295837128</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.0037201062887510573 +/- 0.0019120489942358767</t>
+          <t>-0.007927369353410074 +/- 0.0013642977680026085</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.002302922940655505 +/- 0.0016308195429160298</t>
+          <t>-0.0005757307351638263 +/- 0.0013585351328767046</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.0021700620017714224 +/- 0.0010186005314437405</t>
+          <t>0.002967227635075309 +/- 0.0023354821742135015</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.428697962801653e-05 +/- 0.0006402494373251023</t>
+          <t>-0.00026572187776789934 +/- 0.00021696100467518496</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.857395925593314e-05 +/- 0.0007357505635888484</t>
+          <t>0.0007085916740478537 +/- 0.0019324556447539087</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.004384410983171006 +/- 0.0027475779219213532</t>
+          <t>0.009964570416297613 +/- 0.002892248337866372</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0004428697962799544 +/- 0.0027443637528484803</t>
+          <t>0.018999114260407436 +/- 0.0035948917402268696</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.003675819309123085 +/- 0.0012055498307189006</t>
+          <t>-0.004960141718334798 +/- 0.0030541965721110394</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.004650132860938949 +/- 0.0016241913924616653</t>
+          <t>0.001372896368467702 +/- 0.0014479878409452342</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0010628875110717862 +/- 0.0015367007593354732</t>
+          <t>-0.0013728963684676355 +/- 0.0017089266059853508</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.007351638618246193 +/- 0.0023783386327896473</t>
+          <t>-0.0063773250664304615 +/- 0.0042946954552349455</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.008325952170061967 +/- 0.0022214235968086053</t>
+          <t>-0.0015943312666075848 +/- 0.0031139762322846785</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0017271922054916456 +/- 0.0015398882772996983</t>
+          <t>-0.0016829052258635735 +/- 0.001968654629839939</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.003808680248007157 +/- 0.0012712754733753319</t>
+          <t>0.004074402125775057 +/- 0.0008117937457848995</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0001771479185119995 +/- 0.0011062883965276262</t>
+          <t>-0.0021700620017714558 +/- 0.0022621067828382793</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.0030558015943313198 +/- 0.0014748295664611887</t>
+          <t>-0.0019486271036315173 +/- 0.0017288947117753124</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00022143489813997164 +/- 0.000297086090899031</t>
+          <t>-0.0005757307351638375 +/- 0.0004450786368963958</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.0018600531443754952 +/- 0.0015057573073516367</t>
+          <t>0.010761736049601445 +/- 0.00245822658748945</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.001815766164747501 +/- 0.0007784940580711553</t>
+          <t>0.013330380868024816 +/- 0.0015776362383132687</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.0035872453498670743 +/- 0.0012120400516744219</t>
+          <t>0.00017714791851198842 +/- 0.001106288396527628</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.003011514614703237 +/- 0.0011168751295764986</t>
+          <t>-0.0005314437555358542 +/- 0.0013403672232436953</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.006023029229406507 +/- 0.0012866110758488949</t>
+          <t>0.0012843224092117134 +/- 0.0014614703277236476</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.0005314437555359209 +/- 0.0004339220093504583</t>
+          <t>-0.00022143489813992724 +/- 0.0008912582726969936</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.004340124003542922 +/- 0.0013549210399272213</t>
+          <t>0.0006643046944198483 +/- 0.003139381505482258</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.0013286093888397522 +/- 0.0016922031155485067</t>
+          <t>0.00013286093888398298 +/- 0.0015475115331847673</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.00535872453498667 +/- 0.0006988367510212209</t>
+          <t>-0.002435783879539399 +/- 0.0020511135831548922</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.001771479185119529 +/- 0.0015468776967735003</t>
+          <t>-0.01089459698848536 +/- 0.0027170702657534048</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-4.428697962796102e-05 +/- 0.0004178025302062301</t>
+          <t>0.0005314437555358875 +/- 0.0005875331780965969</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.0003961147878653374</t>
+          <t>0.0013286093888396967 +/- 0.0006860909382121178</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.0007528786536757815 +/- 0.0014560923137974975</t>
+          <t>0.0002657218777679771 +/- 0.0025914506356647907</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.0023029229406554943 +/- 0.0013256536357037871</t>
+          <t>-0.009787422497785626 +/- 0.0015525729090308425</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>-0.0011071744906996916 +/- 0.0004538064998210648</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0007971656333038757 +/- 0.0005531441982638312</t>
+          <t>0.0013286093888397077 +/- 0.0008857395925597977</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.004295837023914917 +/- 0.0015850779599799148</t>
+          <t>-0.008724534986713894 +/- 0.001415105873221475</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0001328609388840163 +/- 0.0013871089250102517</t>
+          <t>-0.00509300265721877 +/- 0.0015500442869796206</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.0001771479185119218 +/- 0.0004931589338202021</t>
+          <t>0.0011514614703277525 +/- 0.0009942402267778504</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.0036315323294950795 +/- 0.001325653635703796</t>
+          <t>0.006155890168290545 +/- 0.0024293335964397766</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.0018600531443755063 +/- 0.0012957253178324066</t>
+          <t>-0.0018157661647475343 +/- 0.0023220065064514287</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0016829052258636624 +/- 0.0009662278223769509</t>
+          <t>0.004118689105403028 +/- 0.0020682541060824625</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.001638618246235557 +/- 0.0011891693163948143</t>
+          <t>-0.010008857395925597 +/- 0.002353468601521081</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.023870682019486233 +/- 0.0028731978004089705</t>
+          <t>-0.03148804251550043 +/- 0.002437393783138546</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.001904340124003512 +/- 0.0008414526129317848</t>
+          <t>0.00088573959255982 +/- 0.001188344363595975</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0008857395925598421 +/- 0.0014688329452415415</t>
+          <t>-0.006510186005314422 +/- 0.0007423850582037456</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4.428697962803874e-05 +/- 0.0004178025302062219</t>
+          <t>0.00022143489813997164 +/- 0.00035705304465449595</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.00022143489813989393 +/- 0.0011759006242118512</t>
+          <t>-0.0006643046944198261 +/- 0.0009753195547185702</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.0012400354295837523 +/- 0.0009863178676403862</t>
+          <t>-0.010318866253321502 +/- 0.0009712892913844703</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-0.0007971656333037646 +/- 0.0012176906186773806</t>
+          <t>0.007307351638618276 +/- 0.0025613806449816196</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.006377325066430439 +/- 0.0014847701164074488</t>
+          <t>0.00022143489813998275 +/- 0.002905779398108831</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.0015943312666075627 +/- 0.0006325445906592248</t>
+          <t>0.0006200177147918761 +/- 0.0006628268178518836</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.0003100088573959714 +/- 0.0004871567759079103</t>
+          <t>0.000752878653675837 +/- 0.0008414526129317941</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-0.006067316209034501 +/- 0.0012843224092116883</t>
+          <t>-0.011293179805137277 +/- 0.0012249173326784157</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-0.011071744906997283 +/- 0.0018893471220284652</t>
+          <t>-0.010097431355181551 +/- 0.0014794768014605771</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.0014614703277236129 +/- 0.0013871089250102457</t>
+          <t>-0.004428697962798922 +/- 0.0026719403240032654</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.000708591674047776 +/- 0.0004516403466423953</t>
+          <t>0.0009743135518157752 +/- 0.0006200177147918475</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-0.003232949512843175 +/- 0.0009086928489230868</t>
+          <t>-0.003542958370239124 +/- 0.0014144127035138506</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-0.006333038086802434 +/- 0.001284322409211699</t>
+          <t>-0.011603188662533192 +/- 0.001724350959604234</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.001018600531443825 +/- 0.000525878746104439</t>
+          <t>-0.0007528786536758036 +/- 0.0009300265721877926</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.002745792736935293 +/- 0.001168370766897519</t>
+          <t>0.0052258635961027755 +/- 0.001505757307351631</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.0009743135518157309 +/- 0.0008356050604124509</t>
+          <t>-0.006643046944198372 +/- 0.0029642516440534054</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.0218777679362267 +/- 0.0024273143677670016</t>
+          <t>-0.025642161204605808 +/- 0.002508770423076808</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.002391496899911372 +/- 0.0009539707364277414</t>
+          <t>-0.005624446412754613 +/- 0.0014827873377133078</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0006643046944198483 +/- 0.00029708609089898133</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.00017714791851191068 +/- 0.0009743135518157662</t>
+          <t>0.0011957484499557469 +/- 0.0013440204522137836</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.004472984942426883 +/- 0.0007784940580711522</t>
+          <t>-0.006687333923826366 +/- 0.0016145018718829196</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0001328609388840163 +/- 0.000793466468873743</t>
+          <t>-0.0029229406554472704 +/- 0.0011411956356709712</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.002878653675819254 +/- 0.0010711591339635019</t>
+          <t>-0.001284322409211669 +/- 0.0016023075744132456</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.0034100974313551412 +/- 0.0009300265721877889</t>
+          <t>-0.004340124003542933 +/- 0.0018558305438225943</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.005978742249778524 +/- 0.0014178751632933704</t>
+          <t>-0.004472984942426916 +/- 0.0013204651475532036</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.0004871567759079376 +/- 0.0003100088573959603</t>
+          <t>-0.0001771479185119329 +/- 0.0003542958370239074</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.00026572187776789934 +/- 0.0005671500653173637</t>
+          <t>0.0028786536758193537 +/- 0.0008689732892094129</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.0009743135518158419 +/- 0.0003860849374261003</t>
+          <t>-0.0016829052258635958 +/- 0.0006803494905109567</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.00044286979627993216 +/- 0.0007922295757306934</t>
+          <t>-4.428697962796102e-05 +/- 0.0005030033964393419</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.005270150575730692 +/- 0.0005757307351638434</t>
+          <t>-0.004915854738706815 +/- 0.0017317285027473157</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>4.428697962799433e-05 +/- 0.00013286093888398298</t>
+          <t>-0.00022143489813992724 +/- 0.00040830577755946996</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0031443755535872087 +/- 0.0006402494373251076</t>
+          <t>-0.005137289636846743 +/- 0.001158254812278301</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.005447298494242647 +/- 0.001329347300248336</t>
+          <t>-0.00394154118689104 +/- 0.0013927533386639919</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.000575730735163893 +/- 0.0005258787461044363</t>
+          <t>4.428697962801653e-05 +/- 0.0003100088573959254</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.006111603188662473 +/- 0.0006803494905109422</t>
+          <t>-0.005048715677590754 +/- 0.0016475708802248322</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.0012400354295836746 +/- 0.000476985368213864</t>
+          <t>-0.001904340124003523 +/- 0.0018584707934771706</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.0005314437555358431 +/- 0.0008117937457848997</t>
+          <t>-0.0032772364924711804 +/- 0.0011411956356709376</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0028071790151863786 +/- 0.0015186378278877098</t>
+          <t>0.0010584445467095803 +/- 0.0013185962983795964</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0003221352968246549 +/- 0.001030051968964545</t>
+          <t>0.002162908421537013 +/- 0.0007714245105495007</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.001288541187298664 +/- 0.00163092914373394</t>
+          <t>-0.0022549470777727177 +/- 0.0010176412511502982</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.0006902899217671287 +/- 0.000854771082420916</t>
+          <t>9.20386562356157e-05 +/- 0.0005366729769760786</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0005522319374137163 +/- 0.0020456613686970003</t>
+          <t>-0.0029452369995398462 +/- 0.0008779928222889598</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.003589507593189123 +/- 0.0017918014113144783</t>
+          <t>0.0033594109526000615 +/- 0.0013965937326731119</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.00023009664058903923 +/- 0.00023009664058903923</t>
+          <t>4.601932811780785e-05 +/- 0.00013805798435342353</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0051081454210768484 +/- 0.0019024414734095188</t>
+          <t>0.004187758858720625 +/- 0.0013408929852124585</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.01803957662218133 +/- 0.002995147739580849</t>
+          <t>0.019880349746893657 +/- 0.002176086593195935</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.01983433041877588 +/- 0.002741531708901315</t>
+          <t>0.020800736309249834 +/- 0.0020248504371836048</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0037735849056603765 +/- 0.0016694300181515904</t>
+          <t>-0.0046019328117810065 +/- 0.002128860286464856</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.0010584445467096137 +/- 0.00217851824731607</t>
+          <t>-0.002991256327657643 +/- 0.001305684395684398</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.001702715140358957 +/- 0.0012356853734098077</t>
+          <t>-0.003451449608835766 +/- 0.0012218976573724603</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-0.0024850437183617123 +/- 0.00253064465437046</t>
+          <t>-0.0042337781868385105 +/- 0.0031130298251795304</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.014035895075931903 +/- 0.0018664795021328367</t>
+          <t>0.0036355269213069084 +/- 0.0013250050666256587</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.005384261389783695 +/- 0.0017469169715694584</t>
+          <t>0.004371836171191868 +/- 0.0011319258054531957</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0018867924528301772 +/- 0.0017151076993634903</t>
+          <t>0.0015646571560054777 +/- 0.0008283479061205634</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0013805798435342909 +/- 0.0010693925484235995</t>
+          <t>-0.0011504832029452738 +/- 0.000776895674925654</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.004417855499309698 +/- 0.0011309899427008304</t>
+          <t>0.0013805798435342575 +/- 0.0012686653246286276</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.601932811780785e-05 +/- 0.0002478216662279941</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.0021168890934192388 +/- 0.001368252991009522</t>
+          <t>-0.005660377358490609 +/- 0.0009442376681400521</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.0024850437183617123 +/- 0.001808272683330741</t>
+          <t>-0.0014726184997699398 +/- 0.0006763432331660961</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0017487344684767425 +/- 0.0011421696866995758</t>
+          <t>0.0007363092498849144 +/- 0.001149562447933417</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.001656695812241149 +/- 0.0008023744028606977</t>
+          <t>0.000598251265531502 +/- 0.000619126739395915</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9.20386562356157e-05 +/- 0.0004956433324559882</t>
+          <t>-0.0006902899217671621 +/- 0.0009487127532484356</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.002024850437183634 +/- 0.0005124495501914521</t>
+          <t>-0.0006902899217671621 +/- 0.000308707037850907</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>-0.0017027151403589459 +/- 0.0016470805493026602</t>
+          <t>0.00046019328117806734 +/- 0.0010290234595028778</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.00161067648412333 +/- 0.001013470572735642</t>
+          <t>0.0034514496088356773 +/- 0.0015974739951872825</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.006948918545789218 +/- 0.0018912768143611938</t>
+          <t>0.0017027151403589125 +/- 0.0015407886831829921</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0011965025310630372 +/- 0.002090716372130788</t>
+          <t>-0.007086976530142686 +/- 0.0011858351336148307</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.0006442705936493098 +/- 0.0003681546249424628</t>
+          <t>0.00013805798435342353 +/- 0.0002946674752615104</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0022089277496548654 +/- 0.0005747812239667303</t>
+          <t>-9.20386562356157e-05 +/- 0.000344377117972739</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.001978831109065815 +/- 0.0016211610633969952</t>
+          <t>-0.002761159687068615 +/- 0.0019306191406721748</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.0006902899217671399 +/- 0.0015018102965559843</t>
+          <t>-0.0015186378278877588 +/- 0.0007984055026643891</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-4.601932811780785e-05 +/- 0.00013805798435342353</t>
+          <t>0.0008283479061205412 +/- 0.00034437711797273893</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>4.601932811780785e-05 +/- 0.0005226790930326804</t>
+          <t>9.20386562356157e-05 +/- 0.0004011872014303285</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>4.601932811781895e-05 +/- 0.0010782673275526752</t>
+          <t>0.00046019328117807845 +/- 0.0005041164818271023</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0024850437183617123 +/- 0.0014869299973679986</t>
+          <t>0.0005982512655314908 +/- 0.0014847920667189728</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.002024850437183623 +/- 0.0005893349505230658</t>
+          <t>0.00027611596870684706 +/- 0.00030525768894204157</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.0011965025310630372 +/- 0.0007188448850351455</t>
+          <t>4.601932811779674e-05 +/- 0.0005226790930327009</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0073630924988495 +/- 0.002158497818602573</t>
+          <t>0.0022549470777726175 +/- 0.001276155050516521</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.002254947077772651 +/- 0.0010382433661001924</t>
+          <t>0.0005522319374136831 +/- 0.0010040232042922792</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.005246203405430294 +/- 0.0005522319374137292</t>
+          <t>0.0018867924528301438 +/- 0.0006652937089185956</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.005798435342843977 +/- 0.0011858351336148298</t>
+          <t>-0.005660377358490598 +/- 0.0007984055026643917</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0007823285780027666 +/- 0.0010504106958594882</t>
+          <t>-0.00013805798435345684 +/- 0.000684126495504777</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.004417855499309698 +/- 0.0007755315023632308</t>
+          <t>-0.001150483202945285 +/- 0.0005541460919830864</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.001242521859180812 +/- 0.00021088705453086413</t>
+          <t>0.0001840773124712314 +/- 0.0003681546249424628</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0055223193741371305 +/- 0.0007700506456825486</t>
+          <t>-0.003819604233778229 +/- 0.0011092471967965054</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.003589507593189145 +/- 0.0012653223271852107</t>
+          <t>-0.0023469857340083222 +/- 0.0010176412511502867</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.008237459733087893 +/- 0.0021233818674752662</t>
+          <t>0.002531063046479487 +/- 0.001584161479802887</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.004279797514956274 +/- 0.0014413676726521827</t>
+          <t>0.0019788311090657706 +/- 0.0008743672342383964</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>9.20386562356157e-05 +/- 0.00027611596870684706</t>
+          <t>-0.0002761159687068693 +/- 0.00036815462494250165</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.0006902899217671177 +/- 0.0005145117297514289</t>
+          <t>0.0009203865623561569 +/- 0.0005041164818271023</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.0009664058904739648 +/- 0.00013805798435342353</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.00644270593649332 +/- 0.001758396058402468</t>
+          <t>0.0023930050621260414 +/- 0.00061051537788412</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.005798435342843977 +/- 0.001271999536225052</t>
+          <t>0.002807179015186345 +/- 0.0008347150090758119</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,147 +1616,147 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.0008283479061205523 +/- 0.0004956433324560109</t>
+          <t>-0.00046019328117811174 +/- 0.000356464182807892</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.003359410952600095 +/- 0.0008245040435880709</t>
+          <t>-0.0040036815462494825 +/- 0.0010504106958594858</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.0015186378278876922 +/- 0.0008982614494221558</t>
+          <t>0.004233778186838422 +/- 0.0009827039348395</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.0001840773124712314 +/- 0.0006242365377933757</t>
+          <t>0.0012885411872986196 +/- 0.0005366729769760786</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.0027611596870685704 +/- 0.0009203865623561791</t>
+          <t>-0.0029912563276576543 +/- 0.000625930534226228</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.005982512655315209 +/- 0.0013805798435343058</t>
+          <t>-0.0006902899217671842 +/- 0.000854771082420943</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.003681546249424772 +/- 0.0013805798435342798</t>
+          <t>-0.004601932811780995 +/- 0.0008970818541011324</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.0007823285780027333 +/- 0.0005062126092958862</t>
+          <t>-0.0015186378278877698 +/- 0.0002946674752615104</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>9.20386562356157e-05 +/- 0.00018407731247123142</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>-0.0015646571560055777 +/- 0.0004217741090617282</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>-0.0018867924528302327 +/- 0.000598251265531502</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>-0.0007823285780028 +/- 0.0006524365797863925</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>-9.2038656235649e-05 +/- 0.000736309249884963</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>-0.001748734468476798 +/- 0.0006442705936493321</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-0.001794753796594617 +/- 0.0005226790930326804</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.00027611596870683595 +/- 0.0006572874761659287</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>-0.0014726184997699509 +/- 0.000495643332456011</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>-0.00041417395306028173 +/- 0.00024782166622801683</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>-0.002761159687068615 +/- 0.0007970781443023006</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>4.601932811780785e-05 +/- 0.00013805798435342353</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>-0.001702715140358957 +/- 0.0010300519689645442</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>-0.0014726184997699066 +/- 0.0013927976024318027</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>-0.001288541187298664 +/- 0.0004956433324560378</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.001978831109065804 +/- 0.0018755346408021007</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>4.601932811781895e-05 +/- 0.0009531668282194062</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>9.20386562356157e-05 +/- 0.0010851197535712458</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>-0.0003681546249424628 +/- 0.0001840773124712314</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>-0.00027611596870684706 +/- 0.00036815462494246273</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-0.0005522319374136941 +/- 0.0004956433324559883</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>-4.601932811780785e-05 +/- 0.0002478216662279941</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>-0.003313391624482287 +/- 0.0010248991003828725</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>4.601932811780785e-05 +/- 0.00013805798435342353</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0011965025310630485 +/- 0.0009249770475030878</t>
+          <t>-4.4408920985006264e-17 +/- 0.0009431155790114778</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.0024390243902439046 +/- 0.0008498014409857093</t>
+          <t>-0.0024850437183617457 +/- 0.0007755315023632071</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.0008283479061205412 +/- 0.00027611596870684706</t>
+          <t>-0.00013805798435343464 +/- 0.0004141739530602916</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.002945236999539802 +/- 0.0007188448850351255</t>
+          <t>-0.0020708697653014753 +/- 0.0008296252359558172</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>-0.0009203865623561791 +/- 0.0009203865623561902</t>
+          <t>-0.0006902899217671842 +/- 0.0005145117297514786</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.001288541187298642 +/- 0.0005366729769761109</t>
+          <t>-0.0018867924528302327 +/- 0.0005226790930326804</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.0005623242736645274 +/- 0.0010006633788220704</t>
+          <t>-0.0010777881911902209 +/- 0.0011677540575798747</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.009512652296157498 +/- 0.0013262391469620331</t>
+          <t>-0.00815370196813493 +/- 0.0016124321025384513</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.005904404873477076 +/- 0.0013613719818494695</t>
+          <t>-0.0035145267104029878 +/- 0.0024371890579092553</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.003889409559512702 +/- 0.0010696075173864583</t>
+          <t>0.004217432052483638 +/- 0.001999131115998286</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.00515463917525778 +/- 0.0015399884465937003</t>
+          <t>-0.0038425492033739017 +/- 0.00138693988631197</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.0059512652296157985 +/- 0.001977595861856526</t>
+          <t>-0.014292408622305497 +/- 0.0014405272866859758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.0004217432052484038 +/- 0.0001405810684161346</t>
+          <t>-0.0002811621368322026 +/- 0.00022956792340982687</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.002249297094657876 +/- 0.0012002107286659372</t>
+          <t>-0.00412371134020616 +/- 0.0022257435964457084</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.006279287722586635 +/- 0.004223675478629349</t>
+          <t>0.031443298969072185 +/- 0.006093468171381693</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.040159325210871524 +/- 0.004751418283115753</t>
+          <t>0.03697282099343959 +/- 0.00512666002842554</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.003420805998125542 +/- 0.0017414155741389027</t>
+          <t>0.003795688847235268 +/- 0.00151772584261495</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.00023430178069356878 +/- 0.0007334805924320067</t>
+          <t>0.00037488284910967005 +/- 0.0021040247723190025</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0004217432052483039 +/- 0.0006091846298031739</t>
+          <t>0.005810684161199675 +/- 0.001990324328172004</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.004123711340206138 +/- 0.0019069343907568597</t>
+          <t>0.010590440487347719 +/- 0.0033082216672395094</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.019212746016869665 +/- 0.004165039558254712</t>
+          <t>0.051546391752577345 +/- 0.003689788132151755</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.010356138706654217 +/- 0.0009705864656611111</t>
+          <t>-0.0037019681349577892 +/- 0.0013653985271165367</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0030459231490159943 +/- 0.001768939652125299</t>
+          <t>-0.010449859418931562 +/- 0.0016902238797442772</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.009372071227741363 +/- 0.0017025212862778773</t>
+          <t>-0.0005154639175257269 +/- 0.002121175313543824</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.0033270852858482193 +/- 0.0009476920532406996</t>
+          <t>-0.0009372071227740974 +/- 0.0014965997584509224</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.00014058106841614572 +/- 0.00030005268216649645</t>
+          <t>0.0004686035613870931 +/- 0.0006627055118899132</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.005014058106841579 +/- 0.0016103880297506702</t>
+          <t>0.0007029053420806175 +/- 0.0019349412204369893</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0042642924086222275 +/- 0.0012652296157450826</t>
+          <t>-0.0019212746016869509 +/- 0.0017211216187635215</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>-0.012980318650421808 +/- 0.0008903467666354209</t>
+          <t>-0.0034676663542642537 +/- 0.001768318862616034</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.005154639175257792 +/- 0.000864062273410749</t>
+          <t>-0.0022492970946578874 +/- 0.0006887037702295774</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.0004217432052484149 +/- 0.0009929531443494725</t>
+          <t>-0.0019212746016869509 +/- 0.0016158331442892694</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.0014526710402999687 +/- 0.0006091846298031885</t>
+          <t>0.00046860356138710423 +/- 0.0007556005387346375</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.0056232427366448515 +/- 0.001291850867112467</t>
+          <t>-0.003186504217432018 +/- 0.0018124723154464507</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.0015463917525772586 +/- 0.0028430761597221</t>
+          <t>-0.01443298969072162 +/- 0.0016999397513792814</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0013120899718837564 +/- 0.001750847393839665</t>
+          <t>-0.004967197750702879 +/- 0.0021289253405061873</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.017900656044985995 +/- 0.0008841594313079949</t>
+          <t>-0.010496719775070263 +/- 0.002219816172882303</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>-0.0006091846298032167 +/- 0.0008395722993050289</t>
+          <t>-4.686035613867823e-05 +/- 0.0006774523099719171</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.0008434864104966744 +/- 0.0004591358468197014</t>
+          <t>-0.0009840674789127978 +/- 0.0005322313351265385</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.01007497656982198 +/- 0.0022692221204879573</t>
+          <t>0.001405810684161224 +/- 0.001802753895189442</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.0013120899718838453 +/- 0.0016474597779987921</t>
+          <t>-0.007544517338331736 +/- 0.002483598875351444</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.0026241799437676126 +/- 0.0006692997590012009</t>
+          <t>-9.372071227738976e-05 +/- 0.00040851911373387</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0018275538894095057 +/- 0.001036239193415923</t>
+          <t>0.0008903467666354636 +/- 0.0012824678709844367</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.0012183692596064223 +/- 0.0015849610614140374</t>
+          <t>-0.0002811621368322137 +/- 0.002344891472014387</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.002249297094657865 +/- 0.0024600571224754845</t>
+          <t>-0.0067947516401124395 +/- 0.0016666747182547978</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.0005623242736645162 +/- 0.001218369259606395</t>
+          <t>0.0005154639175257936 +/- 0.0006442233872946565</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.0032333645735708183 +/- 0.0012477532292122272</t>
+          <t>-0.0020618556701030633 +/- 0.0017806935332708507</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.0014526710402999465 +/- 0.0013492202482556805</t>
+          <t>0.005060918462980357 +/- 0.0019524523576382234</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-0.006419868791002881 +/- 0.0015828815139694841</t>
+          <t>-0.007591377694470447 +/- 0.0010848956797366485</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.010356138706654227 +/- 0.0013492202482556389</t>
+          <t>0.00557638238050614 +/- 0.001602185660475977</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.014807872539831346 +/- 0.002418648153807678</t>
+          <t>-0.002530459231490134 +/- 0.002427710186876972</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.011152764761012235 +/- 0.0015371339706519867</t>
+          <t>-0.012277413308341112 +/- 0.0015932521087160308</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.01368322399250239 +/- 0.002495506458424425</t>
+          <t>-0.015089034676663527 +/- 0.00121836925960637</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.00014058106841614572 +/- 0.0003000526821664965</t>
+          <t>-0.000702905342080573 +/- 0.0005239147088799881</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>-0.009137769447047861 +/- 0.0012960934101161495</t>
+          <t>-0.008716026241799424 +/- 0.0018051884052725634</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.016026241799437735 +/- 0.0018603030216756474</t>
+          <t>-0.004029990627928759 +/- 0.002001326757644103</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.011855670103092842 +/- 0.001886674989615493</t>
+          <t>-0.008247422680412352 +/- 0.0024004214573319187</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.01049671977507034 +/- 0.0020977534475725684</t>
+          <t>0.005810684161199642 +/- 0.003796556532432807</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.0002811621368322581 +/- 0.0004294822581964393</t>
+          <t>0.00014058106841614572 +/- 0.0004217432052483508</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0008434864104967632 +/- 0.0005464809648402456</t>
+          <t>-9.372071227738976e-05 +/- 0.0008841594313080066</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>4.6860356138700435e-05 +/- 0.0001405810684161013</t>
+          <t>0.003795688847235268 +/- 0.0010362391934159105</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.005623242736644862 +/- 0.0023336269162115867</t>
+          <t>-0.01087160262417991 +/- 0.0027627746903437006</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.02169634489222123 +/- 0.0023340973580904013</t>
+          <t>-0.004545454545454519 +/- 0.0020215233936385062</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.005857544517338387 +/- 0.0013621782430879663</t>
+          <t>-0.0011715089034676329 +/- 0.0005239147088799931</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.02347703842549209 +/- 0.002337857485148352</t>
+          <t>-0.01316776007497653 +/- 0.0009929531443494388</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.004217432052483661 +/- 0.002010085341099072</t>
+          <t>-0.003655107778819089 +/- 0.001634076454935595</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0008903467666353971 +/- 0.0006442233872946291</t>
+          <t>-0.0019681349578256403 +/- 0.0010006633788220663</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.02155576382380512 +/- 0.0026006442222139994</t>
+          <t>-0.018041237113402032 +/- 0.0018419160269010052</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.014854732895970047 +/- 0.001778842820628132</t>
+          <t>0.006232427366448012 +/- 0.0021376747381362735</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.012136832239925066 +/- 0.0015031879036874938</t>
+          <t>-0.006466729147141493 +/- 0.002185923859360945</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-0.0004217432052484149 +/- 0.0006091846298031995</t>
+          <t>-0.001546391752577292 +/- 0.0012228667620149936</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.00020956588355199228</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.00028116213683219147 +/- 0.0017558569817427607</t>
+          <t>-0.0008434864104966855 +/- 0.0013053784702140728</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.001405810684161246 +/- 0.0013087385233148073</t>
+          <t>-0.00023430178069350216 +/- 0.001261753703639747</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.0003748828491097034 +/- 0.0006560449859419075</t>
+          <t>-0.00032802249297092523 +/- 0.0005564358991114179</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.002155576382380564 +/- 0.0013287204197523904</t>
+          <t>-0.003373945641986842 +/- 0.0009086560182598642</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.0006560449859419615 +/- 0.0007897047584982561</t>
+          <t>0.0011246485473289992 +/- 0.0011128717982228581</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.00023430178069357987 +/- 0.0008183809370465403</t>
+          <t>-0.0041705716963448495 +/- 0.0010572178231188732</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-0.0007497656982193623 +/- 0.0004294822581964344</t>
+          <t>-4.6860356138700435e-05 +/- 0.0001405810684161013</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.0009840674789127867 +/- 0.0004892364812048075</t>
+          <t>-0.0009840674789127978 +/- 0.0008754236969198387</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>-0.0005623242736645384 +/- 0.0006887037702295759</t>
+          <t>0.0008903467666354526 +/- 0.0016158331442892898</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.0002811621368322692 +/- 0.0004778837407303516</t>
+          <t>-9.372071227740087e-05 +/- 0.00018744142455480174</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.0021087160262417636 +/- 0.0012790388063688783</t>
+          <t>0.0016401124648547706 +/- 0.0018299554067260347</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-0.0014058106841612684 +/- 0.0008382635342079877</t>
+          <t>0.000843486410496741 +/- 0.0005852856605809152</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.0021555763823805528 +/- 0.0008691301307868316</t>
+          <t>-0.004217432052483561 +/- 0.0016097060953437488</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0010777881911903208 +/- 0.0008903467666354326</t>
+          <t>-0.0015932521087159922 +/- 0.001679144598610013</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.00023430178069352436 +/- 0.000480175762228661</t>
+          <t>0.0003748828491096923 +/- 0.00018744142455484614</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.0007497656982193623 +/- 0.0015428376413452974</t>
+          <t>-0.0017806935332708273 +/- 0.001402683181546008</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.0029053420805998597 +/- 0.001448887050959724</t>
+          <t>-0.000796626054357974 +/- 0.001452671040299924</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0005623242736645274 +/- 0.0010223722694129279</t>
+          <t>0.004076850984067504 +/- 0.0014825953157972206</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.001670146137787054 +/- 0.0015270082294705518</t>
+          <t>-0.012943632567849694 +/- 0.002522556570687782</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.010594989561586643 +/- 0.002546737557151548</t>
+          <t>-0.03355949895615867 +/- 0.003563231563402587</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0018267223382045894 +/- 0.0012405912655537434</t>
+          <t>-0.008141962421711946 +/- 0.001870195497616782</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.006889352818371652 +/- 0.0019219157243759947</t>
+          <t>0.009864300626304789 +/- 0.0024418971952588154</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.0013569937369519725 +/- 0.001670146137787043</t>
+          <t>-0.013152400835073075 +/- 0.0019500565440782104</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.00323590814196244 +/- 0.0024234210367941552</t>
+          <t>0.0026096033402922547 +/- 0.00109479002940516</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002334100185281599</t>
+          <t>0.00020876826722338038 +/- 0.000346203005256302</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.008611691022964552 +/- 0.0016380328628888404</t>
+          <t>-0.006106471816283943 +/- 0.002139874739039697</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.021868475991649306 +/- 0.0030022916530834383</t>
+          <t>0.03282881002087683 +/- 0.004588451535297457</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.01654488517745304 +/- 0.003043741818752281</t>
+          <t>0.018789144050104366 +/- 0.004069642732696851</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.0007306889352818313 +/- 0.0010227514583645756</t>
+          <t>-0.007933194154488543 +/- 0.002950583303779249</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>5.2192066805845094e-05 +/- 0.0008235769226544558</t>
+          <t>-0.023799582463465575 +/- 0.002394017733022909</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.0034446764091857762 +/- 0.002064062623516183</t>
+          <t>-0.012630480167014624 +/- 0.0018643602400304393</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.001983298538622125 +/- 0.001819999558889636</t>
+          <t>0.006263048016701444 +/- 0.002800920222337964</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.00020876826722338038 +/- 0.0016537556907885943</t>
+          <t>0.01576200417536533 +/- 0.0025547470251608183</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.008768267223382087 +/- 0.0018199995588896194</t>
+          <t>0.008872651356993722 +/- 0.0023803244782863255</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.001617954070981209 +/- 0.0021194092384391465</t>
+          <t>0.0029749478079331704 +/- 0.0013620029593632342</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.014405010438413367 +/- 0.002204458463668363</t>
+          <t>0.005636743215031293 +/- 0.002320053316377136</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.006837160751565719 +/- 0.001753684511107675</t>
+          <t>-0.017066805845511467 +/- 0.002190202010266947</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>5.2192066805845094e-05 +/- 0.00015657620041753528</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0023486430062630405 +/- 0.0012623576850154456</t>
+          <t>-0.002192066805845494 +/- 0.0011386964629055978</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.001096033402922747 +/- 0.0019591152796579656</t>
+          <t>-0.016649269311064717 +/- 0.003473420278074076</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0012526096033402823 +/- 0.001239492910964282</t>
+          <t>-0.0017223382045928881 +/- 0.0007399502546324484</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0009394572025052117 +/- 0.0008670797351688944</t>
+          <t>0.0053235908141962 +/- 0.001230670785235021</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00026096033402922547 +/- 0.0012405912655537178</t>
+          <t>0.003810020876826692 +/- 0.001793615895348585</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0008350730688935215 +/- 0.0006683845759324423</t>
+          <t>0.0007828810020876764 +/- 0.0007828810020876764</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.0019311064718162795 +/- 0.0015135699373695281</t>
+          <t>0.008402922755741093 +/- 0.0013699796188316302</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.006002087682672197 +/- 0.00157010531904921</t>
+          <t>-0.004801670146137793 +/- 0.002174599859707712</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.004540709812108523 +/- 0.0016347035243596765</t>
+          <t>-0.008924843423799612 +/- 0.0035739182287619904</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.010020876826722336 +/- 0.002378034603318297</t>
+          <t>-0.009498956158663896 +/- 0.004225946237995233</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0005219206680584509 +/- 0.0</t>
+          <t>-0.00010438413361169019 +/- 0.00031315240083507057</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.0015135699373695077 +/- 0.0005927879275365583</t>
+          <t>0.00026096033402922547 +/- 0.00026096033402922547</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,217 +2381,217 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0028183716075156793 +/- 0.0024833772971545806</t>
+          <t>0.005688935281837138 +/- 0.003723237333405391</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.009133611691022957 +/- 0.0014245661862167538</t>
+          <t>0.00010438413361169019 +/- 0.0014350445808838633</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.0005219206680584509 +/- 0.0</t>
+          <t>0.0008350730688935215 +/- 0.0002556878645911439</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.00026096033402922547 +/- 0.00026096033402922547</t>
+          <t>0.00020876826722338038 +/- 0.0006683845759324423</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.0040187891440501165 +/- 0.0009350977488084294</t>
+          <t>0.0009394572025052117 +/- 0.0016471538453089118</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.00015657620041753528 +/- 0.0008431886441233499</t>
+          <t>-0.016910229645093932 +/- 0.0021670709281865</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0008350730688935215 +/- 0.0006683845759324423</t>
+          <t>-0.001096033402922747 +/- 0.0004923789734893804</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.003914405010438405 +/- 0.001462309574751792</t>
+          <t>0.0030793319415448606 +/- 0.0014844950577586407</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.005010438413361129 +/- 0.0016537556907885943</t>
+          <t>-0.001096033402922758 +/- 0.0020935460459427617</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.0030793319415448606 +/- 0.001466030470270149</t>
+          <t>0.0020876826722338038 +/- 0.0022265896667746734</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.0034446764091857983 +/- 0.002590746063881193</t>
+          <t>0.0036012526096033115 +/- 0.0023625198951474293</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.00365344467640919 +/- 0.0014945533468973496</t>
+          <t>-0.031419624217119003 +/- 0.0029963883286862982</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.002296450939457184 +/- 0.0009099997794448097</t>
+          <t>-0.005167014613778709 +/- 0.002726504777997722</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.002296450939457184 +/- 0.0017183797111851979</t>
+          <t>0.004801670146137749 +/- 0.001696041420592045</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.0014091858037578175 +/- 0.0004697286012526059</t>
+          <t>-0.00020876826722338038 +/- 0.000346203005256302</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>-0.005062630480166974 +/- 0.0010187485018759383</t>
+          <t>-0.02959290187891439 +/- 0.0014014323154590235</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.003235908141962396 +/- 0.0015622786583607147</t>
+          <t>-0.0030271398747390376 +/- 0.0029040558962930155</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.007411273486430103 +/- 0.002320053316377123</t>
+          <t>-0.0029227557411273366 +/- 0.002622099517135804</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.004540709812108523 +/- 0.0010708916768623709</t>
+          <t>-0.004906054279749472 +/- 0.0014613778705637056</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.002713987473903945 +/- 0.0006086588616748699</t>
+          <t>-0.001096033402922747 +/- 0.0013296178708618886</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.00031315240083507057 +/- 0.0005811862591680561</t>
+          <t>-0.0018789144050104234 +/- 0.0006683845759324423</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.001148225469728592 +/- 0.00045499988972240484</t>
+          <t>-0.0013048016701461274 +/- 0.0003501150277922399</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.003914405010438438 +/- 0.0019702073160936494</t>
+          <t>-5.2192066805845094e-05 +/- 0.0024751368896407683</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.006419624217118947 +/- 0.0013213975888488581</t>
+          <t>-0.0018267223382045894 +/- 0.002116837138901183</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>-0.0007306889352818313 +/- 0.00041753653444676075</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-0.014352818371607512 +/- 0.002580738061602509</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-0.003288100208768263 +/- 0.0022149368657539753</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.0007828810020876764 +/- 0.0009971280362496163</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.001096033402922747 +/- 0.0012449749939328254</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>0.0020354906054279587 +/- 0.002054140778095435</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-0.015031315240083498 +/- 0.002769624042050416</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>0.0045407098121085345 +/- 0.002022063739854968</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
           <t>-5.2192066805845094e-05 +/- 0.00015657620041753528</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0002334100185281599</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>-5.2192066805845094e-05 +/- 0.0016413554481749752</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>0.0053757828810021115 +/- 0.0027818910169596107</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.00041753653444676075 +/- 0.0005621257627488999</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.002244258872651339 +/- 0.001667697840153479</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0.0025574112734864317 +/- 0.0018445299631599645</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>0.0006263048016701522 +/- 0.00305936344253713</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-0.0026617954070981 +/- 0.0008560135421115132</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>0.00015657620041753528 +/- 0.00033419228796622116</t>
-        </is>
-      </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.001617954070981198 +/- 0.0016904107244991146</t>
+          <t>-0.013465553235908145 +/- 0.002343417987541072</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0013048016701461274 +/- 0.0010759670212989632</t>
+          <t>-0.014718162839248428 +/- 0.001727864859837862</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.001617954070981198 +/- 0.0010555192284006536</t>
+          <t>-0.0012004175365344372 +/- 0.0015135699373695077</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.002296450939457184 +/- 0.0017958925400923921</t>
+          <t>-0.015918580375782865 +/- 0.001870923625149768</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.00041753653444676075 +/- 0.0015447441113725076</t>
+          <t>-0.003810020876826703 +/- 0.001070891676862391</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.00031315240083507057 +/- 0.0014981941643431326</t>
+          <t>-0.011638830897703567 +/- 0.002536018917172494</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>-0.0009394572025052117 +/- 0.0005113757291822878</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0006784968684759862 +/- 0.0005245237798079755</t>
+          <t>0.00036534446764091566 +/- 0.0003341922879662212</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0006784968684759862 +/- 0.00023917409681397723</t>
+          <t>-0.0023486430062630292 +/- 0.0006284757087052297</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,52 +2601,52 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.00031315240083507057 +/- 0.0008152661457105002</t>
+          <t>-0.0034968684759916213 +/- 0.0011446613882808525</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0007741334537678084</t>
+          <t>-0.020041753653444683 +/- 0.0020772180315378596</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00036534446764091566 +/- 0.000619746455482141</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.00015657620041753528 +/- 0.000619746455482141</t>
+          <t>-0.0012004175365344372 +/- 0.0004076330728552501</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.00015657620041753528 +/- 0.0014014323154590235</t>
+          <t>-0.015448851774530259 +/- 0.002693838810138588</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.0008350730688935215 +/- 0.001324486173324574</t>
+          <t>-0.011534446764091877 +/- 0.002635053353103181</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.006367432150313201 +/- 0.0012526096033403018</t>
+          <t>-0.007202505219206723 +/- 0.0015270082294705442</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0013569937369519835 +/- 0.001996986061556265</t>
+          <t>-0.019415448851774552 +/- 0.001849691560195165</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.003914405010438382 +/- 0.0017349446908762555</t>
+          <t>-0.018580375782881 +/- 0.003227479088463551</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0053235908141962 +/- 0.0010120417238864907</t>
+          <t>0.004958246346555295 +/- 0.001811748951744249</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.008117036337895223 +/- 0.0008904182286037489</t>
+          <t>-0.0011326097215667908 +/- 0.0005663048607833954</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.001415762151958455 +/- 0.002947143935062947</t>
+          <t>-0.0006606890042473057 +/- 0.001582166551603608</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.004341670599339331 +/- 0.0017377963793791132</t>
+          <t>-0.0005191127890514458 +/- 0.0011057455888494692</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.003303445021236406 +/- 0.0018639374854300392</t>
+          <t>-0.0006134969325153449 +/- 0.0009450204999764528</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.005851816894761708 +/- 0.0013381261801564404</t>
+          <t>-0.001462954223690438 +/- 0.0010220107516615375</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.006654082114204785 +/- 0.0015284695366400989</t>
+          <t>-0.0019820670127418836 +/- 0.001380720985212645</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.438414346389923e-05 +/- 0.00018876828692779846</t>
+          <t>9.438414346389923e-05 +/- 0.0001887682869277985</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.01576215195847096 +/- 0.002560577624587179</t>
+          <t>-0.004105710240679616 +/- 0.0014629542236904382</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.00745634733364795 +/- 0.0015335608125787421</t>
+          <t>0.01656441717791408 +/- 0.0027553866119858538</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.006418121755545092 +/- 0.0035453780030189597</t>
+          <t>0.014016045304388824 +/- 0.002312411514865509</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4.7192071731960715e-05 +/- 0.0025365464181928772</t>
+          <t>0.006512505899008936 +/- 0.0019204332184404019</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.00353940537989621 +/- 0.0014352908282912245</t>
+          <t>-0.0012269938650306899 +/- 0.0009003673444237446</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.00604058518168944 +/- 0.0012269938650306899</t>
+          <t>-0.0017932987258140853 +/- 0.0008389046170189428</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.008919301557338378 +/- 0.003712609611178273</t>
+          <t>0.01429919773478051 +/- 0.0038573565053174773</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.005993393109957545 +/- 0.0034359587823062543</t>
+          <t>0.008305804624822999 +/- 0.002123118806833778</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.00858895705521472 +/- 0.0015905898580795587</t>
+          <t>-0.0003303445021236473 +/- 0.0011948078245561415</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.010995752713544128 +/- 0.001565895235775076</t>
+          <t>0.0014629542236903824 +/- 0.000954400585944122</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.0006134969325153339 +/- 0.002100444840421699</t>
+          <t>-0.00023596035865974807 +/- 0.0011798017932987404</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.006276545540349188 +/- 0.002322022576714053</t>
+          <t>-0.004719207173194939 +/- 0.0021626124091344173</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00014157621519584885 +/- 0.0003021766983215162</t>
+          <t>-0.00023596035865974807 +/- 0.00023596035865974807</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0027843322321849827 +/- 0.0011257065070199384</t>
+          <t>-2.2204460492503132e-17 +/- 0.001507193904924125</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.0037281736668240083 +/- 0.0016272713213371123</t>
+          <t>0.002925908447380776 +/- 0.0016591218340015973</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.0014157621519584774 +/- 0.00141576215195847</t>
+          <t>0.0003775365738555747 +/- 0.0013480752106734884</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.002925908447380876 +/- 0.0015905898580795587</t>
+          <t>-0.0013213780084945892 +/- 0.0010925754509476515</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.0035865974516281042 +/- 0.00189004099995286</t>
+          <t>-0.002689948088721128 +/- 0.001728157944653212</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.0002831524303916977 +/- 0.0011598117722930307</t>
+          <t>0.000849457291175082 +/- 0.0004623859825923693</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.008966493629070316 +/- 0.0016347813190834342</t>
+          <t>-0.006229353468617327 +/- 0.0015765260111835642</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.003916941953751818 +/- 0.001635462336117383</t>
+          <t>0.006134969325153339 +/- 0.0014621928631269334</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.0024539877300613355 +/- 0.001348075210673474</t>
+          <t>0.004530438886267052 +/- 0.001197600522930597</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.002878716375648893 +/- 0.0013911659247742775</t>
+          <t>0.0013685700802264834 +/- 0.0014070836730415502</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-0.0005663048607833954 +/- 0.0010077468855150017</t>
+          <t>-0.00018876828692779846 +/- 0.0006401444061468006</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.002689948088721095 +/- 0.0009683003552941265</t>
+          <t>0.0002831524303916977 +/- 0.00070630625517206</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.0032090608777725405 +/- 0.0035049447149838845</t>
+          <t>-9.438414346392143e-05 +/- 0.0018374631745098334</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.0016989145823501528 +/- 0.0024081832604385105</t>
+          <t>-2.2204460492503132e-17 +/- 0.0017403576134578246</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.001368570080226539 +/- 0.0006487837227403347</t>
+          <t>0.0002831524303916977 +/- 0.0005663048607833954</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.000849457291175093 +/- 0.0005082741677333243</t>
+          <t>0.00014157621519584885 +/- 0.0005191127890514458</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.0032090608777725293 +/- 0.0011901387647869884</t>
+          <t>0.003680981595091959 +/- 0.001533560812578775</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0015573383671543372 +/- 0.0015800537086157068</t>
+          <t>-0.0025483718735252792 +/- 0.0009717442322781621</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.00014157621519583774 +/- 0.0014321841345439742</t>
+          <t>-0.0004247286455875465 +/- 0.0008022652194431435</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.002737140160453078 +/- 0.0016857547050016018</t>
+          <t>0.000849457291175082 +/- 0.0008389046170189228</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.0015101462954223654 +/- 0.0012087067932860273</t>
+          <t>0.0017932987258140298 +/- 0.001262773776334061</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0025011798017933297 +/- 0.0014780990810161416</t>
+          <t>-0.000991033506370953 +/- 0.0014841137511577493</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-0.006937234544596482 +/- 0.0020138356105098756</t>
+          <t>0.0016045304388862315 +/- 0.0013546673048048222</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.0034450212364323107 +/- 0.001923330238066533</t>
+          <t>0.0013685700802264944 +/- 0.0008559866515911368</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.004294478527607326 +/- 0.0010854176498348112</t>
+          <t>-0.0025955639452572288 +/- 0.0010605099128949745</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.004483246814535102 +/- 0.0009497221235251702</t>
+          <t>0.0011326097215667464 +/- 0.0017682863610377511</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.0007078810759792442 +/- 0.0007078810759792442</t>
+          <t>-0.0007078810759792442 +/- 0.00048357483558092136</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.0007078810759792442 +/- 0.0013879604690753113</t>
+          <t>0.0008494572911750709 +/- 0.0007550731477111563</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.010806984426616328 +/- 0.0018693064955486779</t>
+          <t>-0.008211420481359144 +/- 0.0018179669923792392</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.007928268050967423 +/- 0.0023577151480503916</t>
+          <t>-0.005143935818782508 +/- 0.001238735700651897</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.001604530438886287 +/- 0.002910645388411376</t>
+          <t>0.006465313827276986 +/- 0.0012133044013386124</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.001462954223690438 +/- 0.000774007525571351</t>
+          <t>-0.0009910335063709418 +/- 0.0003303445021236473</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.00368098159509207 +/- 0.0005503494001741739</t>
+          <t>-0.0011798017932987404 +/- 0.0006061931372659409</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0005663048607833954 +/- 0.0006260735800576575</t>
+          <t>-0.0010382255781028916 +/- 0.00018876828692779843</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.0036337895233600538 +/- 0.001828350224427592</t>
+          <t>0.007550731477111827 +/- 0.0008441974431334845</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.015714959886739 +/- 0.00255055575589841</t>
+          <t>-0.014487966021708376 +/- 0.0026109629435814943</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.0020292590844738336 +/- 0.000368581862949823</t>
+          <t>0.0007550731477111827 +/- 0.0005663048607833731</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.004058518168947589 +/- 0.0015680271567565774</t>
+          <t>-0.0024067956583294302 +/- 0.0014841137511577708</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.011090136857008015 +/- 0.0017939195666586123</t>
+          <t>-0.00028315243039170877 +/- 0.0019134624759521747</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.0012741859367626396 +/- 0.0013018512717445862</t>
+          <t>0.00047192071731948503 +/- 0.0009438414346389701</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.005285512033978257 +/- 0.002022112816010254</t>
+          <t>0.0027371401604529776 +/- 0.000985399387344074</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.00604058518168944 +/- 0.0017758270620318085</t>
+          <t>-0.0013213780084945892 +/- 0.0008904182286037489</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.00957999056158566 +/- 0.001715222448833079</t>
+          <t>0.0052383199622462965 +/- 0.0011257065070199822</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.010193487494100983 +/- 0.0022255452803306435</t>
+          <t>-0.0060405851816895395 +/- 0.0013967577713023878</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-0.0007550731477111938 +/- 0.0004812665892961631</t>
+          <t>4.7192071731949615e-05 +/- 0.00014157621519584885</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.0022652194431335817 +/- 0.0010296094492341528</t>
+          <t>-0.0047663992449269 +/- 0.0011257065070199546</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.0034922133081642047 +/- 0.0013213780084945432</t>
+          <t>0.003869749882019757 +/- 0.001489356662393553</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.0008022652194431435 +/- 0.0010771790665892844</t>
+          <t>0.0006606890042472946 +/- 0.0006401444061468006</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-0.011514865502595539 +/- 0.0022652194431335352</t>
+          <t>-0.002831524303916977 +/- 0.001399943083925579</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.001934874941009934 +/- 0.0012915462183486718</t>
+          <t>-0.0032562529495045235 +/- 0.0018573542854322482</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.018452100047192065 +/- 0.0026313547634640275</t>
+          <t>-0.008447380840018892 +/- 0.0015996650549011883</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.0004247286455875465 +/- 0.0004926996936720471</t>
+          <t>-0.00014157621519584885 +/- 0.00030217669832151615</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.000849457291175093 +/- 0.0010510173407890686</t>
+          <t>-0.0005191127890514458 +/- 0.0006134969325153449</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.0005191127890514458 +/- 0.0005760526482177374</t>
+          <t>-0.001085417649834841 +/- 0.0007326179658452202</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,52 +3046,52 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0005663048607833954 +/- 0.0007840135783783083</t>
+          <t>-0.0007550731477111938 +/- 0.0011006988003483477</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-0.007739499764039625 +/- 0.0015680271567566166</t>
+          <t>-0.002831524303916977 +/- 0.002002190036394213</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>9.438414346389923e-05 +/- 0.0001887682869277985</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-0.0015573383671543372 +/- 0.0008966493629070428</t>
+          <t>-0.0003303445021236473 +/- 0.00021626124091344486</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0014157621519584774 +/- 0.0011559649564809673</t>
+          <t>-0.00047192071731950725 +/- 0.0015364625385653318</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.00490797546012266 +/- 0.0014652359316904247</t>
+          <t>-0.004483246814535202 +/- 0.002154874951737783</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0014157621519584884 +/- 0.0008954066050500476</t>
+          <t>0.0006134969325153339 +/- 0.0008455154727309415</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.0023124115148654757 +/- 0.0017714322207761403</t>
+          <t>-9.438414346389923e-05 +/- 0.0011712764177433705</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>-0.009344030202925901 +/- 0.0019088011718883203</t>
+          <t>-0.014063237376120852 +/- 0.0025396175643367038</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0007550731477111938 +/- 0.0014803574460932813</t>
+          <t>4.7192071731949615e-05 +/- 0.0005760526482177373</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.00509193776520509 +/- 0.0010067966291401492</t>
+          <t>0.0006129184347006711 +/- 0.0010123012990845798</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,27 +3111,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.001697312588401667 +/- 0.0012860143042891022</t>
+          <t>-0.003677510608203649 +/- 0.000961625556547426</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.0008486562942008113 +/- 0.001279081562116968</t>
+          <t>-0.0004243281471003724 +/- 0.0010210470451536067</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0030645921735030666 +/- 0.0013376955171250382</t>
+          <t>-0.0006600660066006236 +/- 0.0007660573696026548</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0004714757190004915 +/- 0.001211243053150883</t>
+          <t>-0.001131541725601093 +/- 0.001177745968580569</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.011645450259311674 +/- 0.0016609066434519907</t>
+          <t>0.0075907590759076386 +/- 0.0016120057517471636</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3141,127 +3141,127 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.008580858085808607 +/- 0.0008111574980709897</t>
+          <t>0.0020744931636021537 +/- 0.00135338991932177</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.005516265912305552 +/- 0.002608500932319318</t>
+          <t>0.00787364450730792 +/- 0.0013006236892157982</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.006789250353606824 +/- 0.0022728846380375292</t>
+          <t>0.009853842527109902 +/- 0.002016351228698066</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0035832154644035883 +/- 0.001417566843788099</t>
+          <t>0.003111739745403186 +/- 0.0007364686163042558</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.003441772748703442 +/- 0.0014767053053621661</t>
+          <t>-0.0019801980198019486 +/- 0.000588872984290261</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.004479019330504486 +/- 0.001140347630593834</t>
+          <t>-0.0024045261669023653 +/- 0.0006129184347006207</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.0007543611504007175 +/- 0.0027182527685807706</t>
+          <t>-0.0010843941537010404 +/- 0.001978513461419832</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.01272984441301277 +/- 0.0025651052350279006</t>
+          <t>0.008156529938708213 +/- 0.0037838680296526737</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.0006129184347005822 +/- 0.0012303619378312156</t>
+          <t>0.00862800565770866 +/- 0.0014152127317118022</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.0012258368694011868 +/- 0.0007660573696026248</t>
+          <t>-0.0014144271570013856 +/- 0.0009190753743337027</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.00655351249410655 +/- 0.0006816045400660621</t>
+          <t>-0.00320603488920318 +/- 0.0007832742916471429</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.003347477604903315 +/- 0.0013574898678819377</t>
+          <t>-9.429514380003834e-05 +/- 0.0009844702035748081</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.714757190003027e-05 +/- 0.0002538974449379691</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.001084394153701107 +/- 0.0011558369327799379</t>
+          <t>-0.0016030174446015621 +/- 0.000822046005382504</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0006600660066006902 +/- 0.0014789615409107027</t>
+          <t>0.004290429042904364 +/- 0.0024082211766378483</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.0007072135785006872 +/- 0.0009945791187990923</t>
+          <t>-0.0016030174446015732 +/- 0.0006734020206075169</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0005657708628005853 +/- 0.00046194997506519614</t>
+          <t>-0.00028288543140024823 +/- 0.0004808127782737032</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0008486562942008558 +/- 0.0010500262824761958</t>
+          <t>-0.0006129184347005712 +/- 0.0007319271426808304</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.0018859028760019215 +/- 0.0005164757732250583</t>
+          <t>-0.0003300330033003007 +/- 0.0004243281471004254</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.001037246581800999 +/- 0.0007543611504007689</t>
+          <t>-0.003960396039603908 +/- 0.0009934609856532537</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.0027345591702026993 +/- 0.001442438334821162</t>
+          <t>0.0037246581801037904 +/- 0.0007439761356934943</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.0014615747289014936 +/- 0.000773277674062088</t>
+          <t>0.0012258368694012868 +/- 0.0009238999501303923</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0023573785950023796 +/- 0.0008945622801042049</t>
+          <t>0.0012258368694012868 +/- 0.0008995183417416131</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.00028288543140025935 +/- 0.0003127416115375051</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.0002357378595002735 +/- 0.0005271258787128069</t>
+          <t>-9.429514380008275e-05 +/- 0.00018859028760016548</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,272 +3271,272 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0018387553041017911 +/- 0.001219473564957825</t>
+          <t>-0.0012258368694011868 +/- 0.0009238999501303889</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.004243281471004256 +/- 0.0018138033061453327</t>
+          <t>-0.000377180575200331 +/- 0.0006600660066006744</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>0.0004243281471004723 +/- 0.00014144271570015743</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-4.714757190001917e-05 +/- 0.0004447893037273101</t>
+          <t>-0.0006129184347005712 +/- 0.0005598463973143739</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0006600660066006347 +/- 0.0008995183417415572</t>
+          <t>3.3306690738754695e-17 +/- 0.0005578575938802064</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0.0006600660066006792 +/- 0.0007945450045427876</t>
+          <t>0.003347477604903415 +/- 0.001272984441301272</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9.429514380012715e-05 +/- 0.0005498304474158711</t>
+          <t>-0.0005657708628005187 +/- 0.0005498304474158654</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.0007543611504007175 +/- 0.0007364686163042531</t>
+          <t>-0.0009429514380009274 +/- 0.0009190753743336857</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0052333804809052255 +/- 0.0006481719511960289</t>
+          <t>0.0005186232909005772 +/- 0.0014370344794086135</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0013672795851013887 +/- 0.0008015087223007994</t>
+          <t>0.0005657708628006187 +/- 0.0005888729842902931</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.002357378595002313 +/- 0.0008945622801042166</t>
+          <t>-0.002027345591702001 +/- 0.0012121603142086295</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.0014144271570013856 +/- 0.0013167600229862212</t>
+          <t>-0.005563413484205526 +/- 0.0013794190323741364</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.00396039603960392 +/- 0.00048081277827372493</t>
+          <t>-0.004856199905704806 +/- 0.0007319271426808248</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.00028288543140025935 +/- 0.0011196927946287478</t>
+          <t>-0.005516265912305462 +/- 0.0011167109177111685</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0011786892975011454 +/- 0.00038011587686461286</t>
+          <t>-0.000895803866100875 +/- 0.0005755094585447204</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>0.000518623290900544 +/- 0.0007439761356935049</t>
+          <t>-0.002923149457802865 +/- 0.0009844702035747804</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.006459217350306479 +/- 0.0009673872950817266</t>
+          <t>-0.0014615747289014381 +/- 0.000880789330139991</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0013201320132013362 +/- 0.001964419298066904</t>
+          <t>-0.00023573785950020687 +/- 0.0009488265816831008</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.0051390853371051206 +/- 0.0019941806678506996</t>
+          <t>-0.007449316360207403 +/- 0.0012790815621169657</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
+          <t>0.0006600660066007236 +/- 0.0005250131412381307</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>-4.714757190001917e-05 +/- 0.00033003300330032456</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>-0.0003300330033002896 +/- 0.0007008990451352393</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.0037246581801037904 +/- 0.0014370344794085912</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>-0.0013201320132012807 +/- 0.0006600660066006681</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.003583215464403655 +/- 0.0010584603640095927</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>-0.00028288543140024823 +/- 0.00048081277827372493</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-0.0008486562942008003 +/- 0.0005077948898759651</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>0.0006600660066007236 +/- 0.0007660573696026507</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>0.004526166902404582 +/- 0.0015233846696278506</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-0.00179160773220175 +/- 0.0004619499750651826</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>-0.005139085337105076 +/- 0.0008287786813412046</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>-0.0015087223008014793 +/- 0.0005498304474158711</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>-0.0006600660066006347 +/- 0.00031274161153753194</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>-0.007307873644507246 +/- 0.000823396944675763</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>-0.007449316360207392 +/- 0.0006600660066006776</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>-0.00447901933050443 +/- 0.00087572728057552</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>-0.00023573785950022907 +/- 0.00038011587686461286</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>0.00014144271570015743 +/- 0.0002160573170653634</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>0.0001885902876002099 +/- 0.00023097498753262187</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>-0.0027345591702026993 +/- 0.0005888729842902894</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>-0.0007072135785006651 +/- 0.0004346791351858925</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>-0.004761904761904701 +/- 0.00039163714582357345</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>-0.006364922206506296 +/- 0.0007959426221656839</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>-9.429514380006054e-05 +/- 0.0005888729842902983</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>-0.006223479490806172 +/- 0.0005498304474158711</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>-0.005752003771805703 +/- 0.0005888729842902787</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
           <t>-0.0001885902876001655 +/- 0.0003771805752003726</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>-0.00028288543140025935 +/- 0.00043211463413065417</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>9.429514380010495e-05 +/- 0.0001885902876002099</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>-0.0076379066478076355 +/- 0.0011315417256011235</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-0.0005186232909004884 +/- 0.0011635042601841603</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>0.0007543611504007841 +/- 0.0003127416115375051</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>0.003677510608203671 +/- 0.0010915452053550287</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>0.00023573785950026238 +/- 0.001215822438305292</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.00047147571900050254 +/- 0.00078892977513821</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-0.00023573785950020687 +/- 0.001016683576277601</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>0.001084394153701107 +/- 0.0012303619378311818</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-0.004290429042904253 +/- 0.0012554009387736249</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-0.004384724186704358 +/- 0.0009202838894834467</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>-0.006742102781706727 +/- 0.0007616923348139364</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.007024988213107042 +/- 0.0009056752811079209</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0.0010372465818010545 +/- 0.0006600660066006617</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>-0.004997642621404985 +/- 0.0006734020206075449</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>-0.0013201320132012807 +/- 0.0005077948898759466</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>-0.0015087223008014793 +/- 0.0007543611504007466</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>0.00028288543140029263 +/- 0.00037718057520038094</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>0.0006129184347006267 +/- 0.0003682343081521208</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>-0.00042432814710039455 +/- 0.0003300330033003245</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>0.0011786892975011898 +/- 0.0009945791187990923</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>-0.001697312588401645 +/- 0.0006395407810584967</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>-0.003583215464403544 +/- 0.00048081277827370753</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>-0.0033003300330032405 +/- 0.0009662376959886422</t>
-        </is>
-      </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>-0.00047147571900043597 +/- 0.0005963748534027945</t>
-        </is>
-      </c>
-      <c r="CI7" t="inlineStr">
-        <is>
-          <t>-0.00018859028760014328 +/- 0.00048081277827372276</t>
-        </is>
-      </c>
-      <c r="CJ7" t="inlineStr">
-        <is>
-          <t>-0.006412069778406415 +/- 0.000947654466866653</t>
-        </is>
-      </c>
-      <c r="CK7" t="inlineStr">
-        <is>
-          <t>0.0025459688826025674 +/- 0.0005657708628005612</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.0013448607108549004 +/- 0.0005601298650187714</t>
+          <t>0.0005283381364073137 +/- 0.0007579122880912358</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00014409221902021984 +/- 0.0009125840537944238</t>
+          <t>-0.00019212295869355244 +/- 0.00038424591738710494</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.0010086455331411615 +/- 0.0007877627025387271</t>
+          <t>9.606147934678732e-05 +/- 0.0005999037462438225</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.00321805955811727 +/- 0.0009375226366927675</t>
+          <t>0.00850144092219023 +/- 0.0011171665081280624</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.001152737752161437 +/- 0.0005348476813477686</t>
+          <t>0.001008645533141217 +/- 0.0005014556440399089</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0012487992315082241 +/- 0.0006860161794950103</t>
+          <t>-0.00024015369836692945 +/- 0.0009901790647496704</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0007684918347743208 +/- 0.00023530160833650646</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.0008165225744475757 +/- 0.0007759603468493431</t>
+          <t>-0.0036983669548510843 +/- 0.0008051419123073947</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.0026897214217098454 +/- 0.002915272027952642</t>
+          <t>0.0010086455331412391 +/- 0.0018903620224932245</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.004610951008645581 +/- 0.0037278785613702537</t>
+          <t>0.000288184438040362 +/- 0.0032731460206341725</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.003025936599423573 +/- 0.0016645267484306898</t>
+          <t>-0.0035062439961574985 +/- 0.0018731988472622488</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.00024015369836692945 +/- 0.0005369999945964842</t>
+          <t>-0.0015850144092219077 +/- 0.00030754679334452144</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0006724303554275224 +/- 0.0004898193576938327</t>
+          <t>4.803073967338811e-05 +/- 0.0007877627025387414</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.021805955811719437 +/- 0.0037216850389645627</t>
+          <t>-0.02055715658021131 +/- 0.0031554404813942</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.012680115273775262 +/- 0.0015519206936987053</t>
+          <t>0.014553314121037475 +/- 0.0016645267484306889</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.0006243996157540566 +/- 0.0008333021888999744</t>
+          <t>-0.003073967339097017 +/- 0.0010346137957991397</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0011047070124879266 +/- 0.0008333021888999698</t>
+          <t>0.0004322766570605263 +/- 0.0005455243367723701</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0010739999891929881</t>
+          <t>-0.0012007684918347362 +/- 0.000536999994596504</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.0011047070124880598 +/- 0.0004827029597080247</t>
+          <t>2.2204460492503132e-17 +/- 0.0006443999935157843</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00048030739673399214 +/- 0.0</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.002977905859750285 +/- 0.0007378622236184944</t>
+          <t>0.00019212295869356356 +/- 0.0006150935866890204</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.0010566762728146605 +/- 0.0011527377521613831</t>
+          <t>0.000960614793467851 +/- 0.0005683073758981416</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.0006243996157541343 +/- 0.0008605414441483712</t>
+          <t>0.00014409221902016433 +/- 0.00030754679334449894</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.0008165225744476978 +/- 0.00037513206896766055</t>
+          <t>0.0004322766570605263 +/- 0.0005014556440399079</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0017291066282421497 +/- 0.00023530160833656086</t>
+          <t>0.0004322766570605263 +/- 0.0004531210918375049</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.00014409221902019764 +/- 0.00022010450023807044</t>
+          <t>0.0006243996157540898 +/- 0.0005283381364073177</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.006724303554274802 +/- 0.0015188653507052744</t>
+          <t>0.003025936599423662 +/- 0.0008333021888999782</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.0017771373679155377 +/- 0.0005283381364073177</t>
+          <t>0.002833813640730087 +/- 0.0008165225744476417</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.0013448607108550114 +/- 0.001132548138573656</t>
+          <t>0.002641690682036546 +/- 0.0007204610951008587</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.0007204610951008327 +/- 0.0006532886891803582</t>
+          <t>-0.0010086455331411947 +/- 0.0007877627025387453</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0003362151777137945 +/- 0.00022010450023807044</t>
+          <t>-0.0003362151777137168 +/- 0.00022010450023801956</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00019212295869359687 +/- 0.00023530160833656086</t>
+          <t>0.0006724303554274779 +/- 0.00023530160833656086</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,107 +3716,107 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.0007204610951009327 +/- 0.00024015369836694056</t>
+          <t>0.0021133525456292434 +/- 0.0012188835293419607</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.0021133525456292547 +/- 0.0009412064333460746</t>
+          <t>0.001969260326609057 +/- 0.0009713615953965811</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>-0.0003842459173871049 +/- 0.00019212295869355244</t>
+          <t>-0.0003362151777137168 +/- 0.00022010450023801956</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.00014409221902014213 +/- 0.00037513206896767334</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0017291066282421387 +/- 0.0008645533141210353</t>
+          <t>0.001969260326609046 +/- 0.0009226403800335592</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.0010086455331411836 +/- 0.0010401732866334187</t>
+          <t>0.0022094140249760198 +/- 0.000780407147419402</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.001536983669548575 +/- 0.000560129865018777</t>
+          <t>0.000624399615754101 +/- 0.00037513206896768613</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.00028818443804038416 +/- 0.0008094284124088701</t>
+          <t>-0.001152737752161359 +/- 0.0010120704853845194</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0003362151777137834 +/- 0.001053396359244061</t>
+          <t>0.0025456292026897476 +/- 0.0009375226366927447</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.00043227665706049303 +/- 0.0005014556440398621</t>
+          <t>4.803073967339922e-05 +/- 0.00045312109183748837</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.01911623439000957 +/- 0.002521499471355743</t>
+          <t>-0.010086455331412081 +/- 0.0014881780388885269</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.0009606147934678733 +/- 0.0009362914836512213</t>
+          <t>-0.0012968299711815456 +/- 0.0009855083827417584</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0014889529298751758 +/- 0.0007268369812882798</t>
+          <t>0.0008645533141210637 +/- 0.0004187222808396604</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0016810758885687505 +/- 0.0006532886891803827</t>
+          <t>0.0007204610951008883 +/- 0.0004428215397355111</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00021479999783860856</t>
+          <t>0.0012007684918348028 +/- 0.0003221999967579004</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.001825168107588948 +/- 0.0003594291437823362</t>
+          <t>-0.00019212295869354136 +/- 0.0008908375115750167</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.005955811719500414 +/- 0.001652704181948619</t>
+          <t>-0.006628242074927915 +/- 0.0010256559319914787</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.014601344860710786 +/- 0.0015519206936987055</t>
+          <t>-0.00475504322766569 +/- 0.0007877627025387441</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.006580211335254516 +/- 0.003015244210512854</t>
+          <t>-0.0030739673390970056 +/- 0.002017291066282409</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0013928914505284106 +/- 0.0005014556440399089</t>
+          <t>0.0003842459173871271 +/- 0.0005601298650187599</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0006724303554275446 +/- 0.00023530160833650646</t>
+          <t>9.606147934677622e-05 +/- 0.00019212295869355244</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.03381364073006719 +/- 0.0013787416036894643</t>
+          <t>-0.0005763688760806795 +/- 0.0012487992315081832</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.010854947166186301 +/- 0.0014912751869606364</t>
+          <t>-0.01243996157540823 +/- 0.0012236060713599539</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,42 +3841,42 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>4.803073967339922e-05 +/- 0.00014409221902019764</t>
+          <t>-0.0006243996157540455 +/- 0.00037513206896763637</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.0009125840537944852 +/- 0.0003362151777137168</t>
+          <t>0.000624399615754101 +/- 0.0004322766570605362</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.00883765609990388 +/- 0.001994288135641381</t>
+          <t>-0.006964457252641665 +/- 0.0012385972102043803</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0012968299711816234 +/- 0.0004827029597080302</t>
+          <t>0.00024015369836695167 +/- 0.0003221999967579004</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0012968299711815234 +/- 0.0008051419123074066</t>
+          <t>0.0004322766570605263 +/- 0.0004531210918375049</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.0037944284341978494 +/- 0.001697463693282649</t>
+          <t>-0.007012487992315053 +/- 0.0008645533141210292</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>0.001536983669548575 +/- 0.0012852150009855646</t>
+          <t>0.0022094140249760085 +/- 0.0010346137957991447</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.00014409221902013104 +/- 0.0007759603468493466</t>
+          <t>-0.0021613832853025873 +/- 0.0006532886891803583</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3886,32 +3886,32 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.00024015369836700718 +/- 0.0007818837942411014</t>
+          <t>0.0005763688760807128 +/- 0.0008263520909743117</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.004514889529298694 +/- 0.001160715271238655</t>
+          <t>-0.0006243996157540676 +/- 0.0005703334335753061</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0012968299711816123 +/- 0.0006461875142686943</t>
+          <t>-0.0008645533141210082 +/- 0.0004187222808396477</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.0038424591738713265 +/- 0.0008591999913543846</t>
+          <t>-0.0012007684918347583 +/- 0.0007818837942410981</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.0012968299711815124 +/- 0.001177488056880998</t>
+          <t>0.002929875120076908 +/- 0.0005455243367723565</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.0017291066282421497 +/- 0.0007502641379353183</t>
+          <t>-0.0015369836695484974 +/- 0.0010479070235000704</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9.606147934682063e-05 +/- 0.00035942914378234516</t>
+          <t>-0.00019212295869355244 +/- 0.00023530160833650646</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>4.8030739673421416e-05 +/- 0.00033621517771375957</t>
+          <t>-0.0005763688760806573 +/- 0.0004187222808396171</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.00014409221902016433 +/- 0.0003075467933444989</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.0020172910662823672 +/- 0.0017423974204819391</t>
+          <t>-0.0013448607108549116 +/- 0.0007979465766491886</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>9.606147934679843e-05 +/- 0.00019212295869359687</t>
+          <t>0.0013928914505283662 +/- 0.0003362151777137168</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.006292026897214286 +/- 0.0016422018249067007</t>
+          <t>0.0024015369836695834 +/- 0.0006443999935157926</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.0006724303554275334 +/- 0.0010994738849433089</t>
+          <t>-0.00014409221902015324 +/- 0.0007140282779692005</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.0004803073967339699 +/- 0.00030377307014107174</t>
+          <t>0.0009125840537944407 +/- 0.0005455243367723731</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0013928914505283996 +/- 0.0006603135007141015</t>
+          <t>-0.0014889529298751092 +/- 0.0005455243367723604</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.005427473583093223 +/- 0.0006094417646709747</t>
+          <t>-4.803073967339922e-05 +/- 0.0005862898950880657</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0010086455331412725 +/- 0.0009713615953966041</t>
+          <t>0.0003842459173871493 +/- 0.0007378622236185073</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.0016957364341085301 +/- 0.0010887696247211373</t>
+          <t>0.0011627906976744208 +/- 0.00044404803245696203</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.003197674418604568 +/- 0.0018024297710986428</t>
+          <t>-0.0018895348837209337 +/- 0.000764521988278078</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0029069767441859628 +/- 0.0008666930145347665</t>
+          <t>0.001017441860465107 +/- 0.0010035036423065745</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0029069767441859628 +/- 0.001039128420035199</t>
+          <t>0.0007267441860465129 +/- 0.0007583563877179533</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0014050387596898696 +/- 0.0010492445652958698</t>
+          <t>-0.0001453488372093026 +/- 0.0004869125785426797</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.0009205426356589163 +/- 0.0014282367221883432</t>
+          <t>0.0009205426356588941 +/- 0.001093073078747881</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>9.689922480620173e-05 +/- 0.00019379844961240348</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0008720930232557822 +/- 0.001278188561848113</t>
+          <t>9.689922480620173e-05 +/- 0.0009141454585326182</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.032945736434108475 +/- 0.003056552382865801</t>
+          <t>0.035852713178294526 +/- 0.002479938738773207</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.04345930232558136 +/- 0.0031327835582029536</t>
+          <t>0.042296511627906944 +/- 0.0019864341085271357</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.005377906976744085 +/- 0.001991155289538232</t>
+          <t>-0.0007751937984496138 +/- 0.0007568071391382431</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.0020833333333332704 +/- 0.0008121634987519019</t>
+          <t>-0.0002906976744186052 +/- 0.0008164873811217416</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.003246124031007669 +/- 0.0013882314711137686</t>
+          <t>0.0009205426356589053 +/- 0.0007946327261073732</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0173934108527131 +/- 0.0032749214372327943</t>
+          <t>0.005087209302325491 +/- 0.0022439023598661506</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.045300387596899194 +/- 0.00372936151122594</t>
+          <t>0.04336240310077516 +/- 0.0017367682489278055</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0004844961240309864 +/- 0.0011867682862321258</t>
+          <t>-0.0005813953488372104 +/- 0.0014502548010751739</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.000678294573643401 +/- 0.0007251274005375675</t>
+          <t>0.000339147286821706 +/- 0.0006868918061413687</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.000678294573643401 +/- 0.0007251274005375601</t>
+          <t>0.0005813953488372104 +/- 0.00042237392863766295</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.0007751937984496138 +/- 0.0007872130237050363</t>
+          <t>0.0005813953488372104 +/- 0.0008612591489646904</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00019379844961240345 +/- 0.0002373536572464324</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.0036821705426355656 +/- 0.0017893590419204666</t>
+          <t>0.0004844961240309975 +/- 0.0011258672518044551</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0010658914728681856 +/- 0.0012781885618481136</t>
+          <t>0.0018410852713177882 +/- 0.0009141454585325724</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.001356589147286824 +/- 0.0009394728405845616</t>
+          <t>-0.002713178294573648 +/- 0.0013737836122827375</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.0009205426356588831 +/- 0.0014117056477066904</t>
+          <t>0.0005329457364340983 +/- 0.0007946327261073745</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.0005329457364341095 +/- 0.0007004279212597377</t>
+          <t>-0.004069767441860472 +/- 0.0009494146289857296</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0009205426356589163 +/- 0.00040245270653672916</t>
+          <t>-0.000339147286821706 +/- 0.0003784035695691215</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>-0.00043604651162790773 +/- 0.0010035036423065899</t>
+          <t>-0.004457364341085279 +/- 0.002371557800488457</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.009399224806201456 +/- 0.002091766777608812</t>
+          <t>4.844961240310086e-05 +/- 0.0009798327721006162</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.004069767441860361 +/- 0.0011300294369855253</t>
+          <t>0.0017441860465115754 +/- 0.0011090623199863485</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.002567829457364279 +/- 0.0015328771336779066</t>
+          <t>0.0 +/- 0.0008666930145348037</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.00043604651162789667 +/- 0.0006298449612402848</t>
+          <t>0.000339147286821706 +/- 0.0003102288874725223</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.00019379844961240345 +/- 0.0003213783711584695</t>
+          <t>0.000339147286821706 +/- 0.00037840356956912144</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.007461240310077421 +/- 0.0012484591789462352</t>
+          <t>-0.001744186046511631 +/- 0.0008164873811217417</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.0030523255813952655 +/- 0.001747547364037906</t>
+          <t>-0.00029069767441861625 +/- 0.0012855134846338548</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.001017441860465107 +/- 0.0004570727292662868</t>
+          <t>9.689922480620173e-05 +/- 0.00042237392863766295</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0005329457364341095 +/- 0.000666072048685443</t>
+          <t>9.689922480620173e-05 +/- 0.00019379844961240348</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.0008236434108526813 +/- 0.0011269092393035455</t>
+          <t>-0.003730620155038766 +/- 0.001126909239303588</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.009593023255813859 +/- 0.001513614278276486</t>
+          <t>0.003197674418604568 +/- 0.0008164873811217073</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0008720930232558044 +/- 0.0008335586499072056</t>
+          <t>0.0007751937984496138 +/- 0.0004440480324569621</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.0003875968992248069 +/- 0.0004747073144928648</t>
+          <t>-0.0018895348837209337 +/- 0.0008516664646921985</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0008720930232558044 +/- 0.0006427567423169207</t>
+          <t>-0.0006298449612403112 +/- 0.001017441860465118</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0020833333333332704 +/- 0.000970202732291661</t>
+          <t>0.0015019379844961045 +/- 0.0008516664646921682</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.004990310077519278 +/- 0.0013188621694589363</t>
+          <t>0.0033430232558138706 +/- 0.0010035036423065588</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.00901162790697665 +/- 0.0009243596912954917</t>
+          <t>-0.0037790697674418674 +/- 0.0013144050354893953</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.00130813953488369 +/- 0.000752140246911782</t>
+          <t>0.0007267441860465019 +/- 0.0011917028949853393</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.001017441860465118 +/- 0.0004570727292663091</t>
+          <t>0.0003875968992248069 +/- 0.0010116576074525746</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0001453488372093026 +/- 0.00022202401622848102</t>
+          <t>9.689922480620173e-05 +/- 0.00019379844961240348</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.002180232558139461 +/- 0.0008999116095448554</t>
+          <t>-0.0009205426356589163 +/- 0.0005058288037262872</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.004844961240309975 +/- 0.0010162876435757303</t>
+          <t>-0.0001453488372093026 +/- 0.0008121634987519496</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.00847868217054254 +/- 0.0008999116095449003</t>
+          <t>0.0012112403100774994 +/- 0.0010887696247211026</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.021656976744185975 +/- 0.0017873901885365067</t>
+          <t>0.0030523255813952764 +/- 0.0015019379844960878</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.00043604651162790773 +/- 0.0006298449612403112</t>
+          <t>-9.689922480620173e-05 +/- 0.00019379844961240348</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>9.689922480620173e-05 +/- 0.0005218182952649723</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-9.689922480620173e-05 +/- 0.00019379844961240348</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.009980620155038667 +/- 0.0018537913245842079</t>
+          <t>0.002810077519379772 +/- 0.0008880960649138854</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0003875968992247958 +/- 0.0012024877563944461</t>
+          <t>-0.0009205426356589163 +/- 0.000764521988278078</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>0.0005813953488372104 +/- 0.0004747073144928648</t>
+          <t>-0.00019379844961240345 +/- 0.0002373536572464324</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.0005329457364341095 +/- 0.00033914728682170607</t>
+          <t>-0.0002422480620155043 +/- 0.0006589859742604392</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0.002470930232558066 +/- 0.001492531182243128</t>
+          <t>-0.004166666666666674 +/- 0.0007251274005375868</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.0006298449612403112 +/- 0.0004869125785426797</t>
+          <t>-9.689922480620173e-05 +/- 0.0002906976744186052</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.005184108527131681 +/- 0.0015929537037571344</t>
+          <t>0.0005329457364341095 +/- 0.0005914028883591921</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>0.01303294573643402 +/- 0.0020720353469324744</t>
+          <t>0.007073643410852615 +/- 0.0014405105375308656</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.022819767441860393 +/- 0.0020945703799629192</t>
+          <t>0.007073643410852615 +/- 0.0008986064433619884</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.0012596899224806223 +/- 0.00038759689922480685</t>
+          <t>0.0009689922480620172 +/- 0.00048449612403100867</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>4.844961240310086e-05 +/- 0.0001453488372093026</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>9.689922480620173e-05 +/- 0.000678294573643412</t>
+          <t>-0.0005329457364341095 +/- 0.0011352107087073645</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.0004844961240310086 +/- 0.0005732635448739948</t>
+          <t>-0.0008720930232558155 +/- 0.0004747073144928648</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.0007267441860465129 +/- 0.0003250098804505514</t>
+          <t>0.0007751937984496138 +/- 0.0002373536572464324</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.0004844961240310086 +/- 0.0012818562553607536</t>
+          <t>-0.0005329457364341095 +/- 0.0006298449612403112</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.001356589147286802 +/- 0.0004223739286376323</t>
+          <t>0.000678294573643412 +/- 0.00038759689922480685</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.0010658914728681967 +/- 0.0007751937984495818</t>
+          <t>0.0021317829457363933 +/- 0.0006204577749449979</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0001453488372093026 +/- 0.00022202401622848102</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.000339147286821706 +/- 0.0003784035695691215</t>
+          <t>0.0002422480620155043 +/- 0.0003250098804505514</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9.689922480620173e-05 +/- 0.00019379844961240348</t>
+          <t>0.0001453488372093026 +/- 0.00037840356956912144</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.00019379844961240345 +/- 0.00044404803245696203</t>
+          <t>-4.844961240310086e-05 +/- 0.0001453488372093026</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0033914728682170603 +/- 0.0006851809895218495</t>
+          <t>-0.0052810077519379935 +/- 0.0007004279212597377</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>-4.844961240310086e-05 +/- 0.0001453488372093026</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>-0.0001453488372093026 +/- 0.0005329457364341095</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>-4.844961240310086e-05 +/- 0.0004570727292663091</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>0.0002422480620155043 +/- 0.00024224806201550433</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>0.0002422480620154932 +/- 0.0008179235957429112</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>4.844961240310086e-05 +/- 0.0007645219882780779</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>0.0012112403100774994 +/- 0.0004964607929243676</t>
-        </is>
-      </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.00281007751937985 +/- 0.0007442970685919208</t>
+          <t>-0.002470930232558144 +/- 0.0007645219882780779</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.0016957364341084746 +/- 0.0010887696247210902</t>
+          <t>-0.000678294573643412 +/- 0.0006204577749450446</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.001356589147286802 +/- 0.0003625637002687578</t>
+          <t>0.0016472868217054294 +/- 0.0003213783711584695</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0023097112860892 +/- 0.0010809060515471966</t>
+          <t>-0.0039370078740157185 +/- 0.0013123359580052441</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.00047244094488191335 +/- 0.0008609564024596738</t>
+          <t>-0.0009973753280839493 +/- 0.001008366021642951</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.002782152230971102 +/- 0.0009693535597175529</t>
+          <t>3.3306690738754695e-17 +/- 0.0010232854955179828</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.006141732283464529 +/- 0.0018039727325395768</t>
+          <t>-0.011968503937007846 +/- 0.0015887397323277159</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.005984251968503884 +/- 0.0009736082409969237</t>
+          <t>-0.003832020997375285 +/- 0.001741801577221744</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.007034120734908111 +/- 0.0014318300994211072</t>
+          <t>-0.009396325459317557 +/- 0.00159997382195571</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.249343832021136e-05 +/- 0.000282685816647488</t>
+          <t>-5.249343832021136e-05 +/- 0.0001574803149606341</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.007716535433070837 +/- 0.0010511802831759038</t>
+          <t>-0.003937007874015708 +/- 0.0021675404537598473</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-0.00031496062992123484 +/- 0.0013526612836456786</t>
+          <t>-0.005564304461942227 +/- 0.0023381687612934435</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.0049343832020997125 +/- 0.0018062625232635255</t>
+          <t>-0.003202099737532771 +/- 0.002066001958441411</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.003937007874015741 +/- 0.0007139879532144779</t>
+          <t>0.00325459317585306 +/- 0.0016566649698750106</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.002782152230971091 +/- 0.0008799503734509529</t>
+          <t>0.001732283464566975 +/- 0.0010246310391571472</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.008503937007873974 +/- 0.0016399474385105836</t>
+          <t>-0.02509186351706033 +/- 0.0020438763605177624</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.054908136482939594 +/- 0.0061000898882242445</t>
+          <t>-0.07863517060367452 +/- 0.006668113179296767</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.050656167979002596 +/- 0.003379615454660334</t>
+          <t>-0.05685039370078737 +/- 0.004636392119002943</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.0001574803149606119 +/- 0.0008149173068902872</t>
+          <t>0.00015748031496064517 +/- 0.0009404972633684514</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.0032545931758529933 +/- 0.0011690843806467545</t>
+          <t>-0.00020997375328081215 +/- 0.0014884458665362554</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.0003149606299212238 +/- 0.0013728815570206757</t>
+          <t>-0.006771653543307055 +/- 0.0011368193085410975</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0004199475065616576 +/- 0.0006556428344775074</t>
+          <t>-0.0034120734908136274 +/- 0.0010821799542303856</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.00010498687664042272 +/- 0.00020997375328084543</t>
+          <t>-0.0006299212598425141 +/- 0.00020997375328080103</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.0030971128608923482 +/- 0.0019982011874723656</t>
+          <t>-0.01207349081364827 +/- 0.002614152146559309</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.0019422572178477981 +/- 0.0010770753033429424</t>
+          <t>-0.0009973753280839493 +/- 0.000828332484937482</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0006299212598425364 +/- 0.000565371633294976</t>
+          <t>0.013070866141732317 +/- 0.00159997382195572</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.0013123359580052175 +/- 0.001451896764928008</t>
+          <t>-0.0006299212598424808 +/- 0.0010960951715391462</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.249343832020026e-05 +/- 0.0009227504373357974</t>
+          <t>0.00020997375328087874 +/- 0.0014124539681967144</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0007349081364828924 +/- 0.000419947506561641</t>
+          <t>-0.0011548556430445722 +/- 0.0006121734272803285</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.000997375328084038 +/- 0.0014930669452312799</t>
+          <t>0.0003149606299212793 +/- 0.0009152543713471243</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.00010498687664045603 +/- 0.001017885534365617</t>
+          <t>-0.002204724409448788 +/- 0.0021102101041723595</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.0045144356955380775 +/- 0.0011784747674878637</t>
+          <t>-0.0014698162729658514 +/- 0.0021361669238189915</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.00414698162729662 +/- 0.0013372954543681818</t>
+          <t>0.005669291338582705 +/- 0.0019613167130991477</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.0007874015748030927 +/- 0.0010564100681101235</t>
+          <t>-0.0005249343832020803 +/- 0.00040661242479864666</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0 +/- 0.00040661242479868965</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,217 +4606,217 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.005144356955380602 +/- 0.0009331437708468055</t>
+          <t>0.005564304461942282 +/- 0.002658055412319596</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0003674540682414462 +/- 0.0013496021136149517</t>
+          <t>0.0005249343832021247 +/- 0.0017251104173391279</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.0002624671916010568 +/- 0.0002624671916010568</t>
+          <t>-5.249343832021136e-05 +/- 0.0005480475857695971</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.249343832021136e-05 +/- 0.000282685816647488</t>
+          <t>0.000419947506561702 +/- 0.0006964041554551971</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.00047244094488190224 +/- 0.0006824146981627477</t>
+          <t>-0.0036220472440944397 +/- 0.0011843059498874897</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>-0.0008923884514435265 +/- 0.0012433301083807802</t>
+          <t>0.003517060367454072 +/- 0.0019507510945997045</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.0001574803149606341 +/- 0.0003361220072143316</t>
+          <t>-0.0001574803149606119 +/- 0.0006660670624907763</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.0008923884514435376 +/- 0.0006660670624907579</t>
+          <t>-0.003779527559055096 +/- 0.0014046286782424921</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0012598425196850727 +/- 0.0015782988323751134</t>
+          <t>0.0010498687664042162 +/- 0.001101111651622209</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.0001574803149606119 +/- 0.0009404972633684385</t>
+          <t>0.0027296587926509573 +/- 0.0014046286782424856</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.026719160104986907 +/- 0.0015999738219557042</t>
+          <t>0.01952755905511815 +/- 0.0016732154803684274</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0004199475065616576 +/- 0.0012598425196850283</t>
+          <t>-0.00036745406824142404 +/- 0.0014670014291319781</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.0012598425196849838 +/- 0.0005353301326606434</t>
+          <t>0.006666666666666732 +/- 0.0006660670624908062</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.003884514435695552 +/- 0.0014124539681967202</t>
+          <t>-0.011968503937007857 +/- 0.0009622206183634564</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>0.00036745406824147955 +/- 0.0004099868596276567</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>-0.0019947506561679208 +/- 0.0006556428344775394</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.008451443569553841 +/- 0.001493066945231278</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.006089238845144407 +/- 0.0022047244094488346</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.0002624671916010901 +/- 0.0009750223423100445</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-0.00020997375328082323 +/- 0.0005353301326606391</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.00047244094488190224 +/- 0.000282685816647488</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>-5.249343832020026e-05 +/- 0.0004952221066696288</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>0.007454068241469869 +/- 0.0019187051845141164</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>0.0061942257217848075 +/- 0.002043876360517794</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.001889763779527609 +/- 0.0003482020777276102</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>0.00036745406824147955 +/- 0.0004099868596276567</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>-0.00446194225721781 +/- 0.0011560480601335936</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>0.019160104986876682 +/- 0.0008545312648871122</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.0008398950131233817 +/- 0.00034820207772761025</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.001469816272965907 +/- 0.001070660265321325</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>0.012493438320209993 +/- 0.0022122107617538554</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-0.0029396325459317254 +/- 0.0012016297262215118</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-0.0007874015748031149 +/- 0.0008216522751967487</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>-0.00015748031496062297 +/- 0.0003361220072143022</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.009186351706036777 +/- 0.0024537524183769655</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>-0.002467191601049823 +/- 0.0014480959815363508</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>5.249343832024467e-05 +/- 0.0010872606392235001</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.01097112860892393 +/- 0.001913672035019224</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0.0012598425196850838 +/- 0.0017441729895890917</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>0.00047244094488191335 +/- 0.0022078468078544013</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
           <t>-5.249343832021136e-05 +/- 0.0001574803149606341</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.00010498687664044493 +/- 0.0008064195010885573</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>-0.002939632545931703 +/- 0.0016298346137805842</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.009081364829396366 +/- 0.0028273455138047537</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>0.0033070866141732824 +/- 0.001409524575548295</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-5.249343832021136e-05 +/- 0.0001574803149606341</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>-5.249343832020026e-05 +/- 0.0004952221066696288</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>-0.0011023622047243498 +/- 0.0005962108499527691</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>0.004041994750656208 +/- 0.0011270819188232855</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0.003989501312335997 +/- 0.0013112856689550326</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>0.00414698162729662 +/- 0.0009521447321373623</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>0.029186351706036794 +/- 0.0018514637363305358</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>5.249343832021136e-05 +/- 0.0001574803149606341</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-0.0006299212598424697 +/- 0.0012377770207403116</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>0.0030446194225722035 +/- 0.0016059903979819747</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-0.001732283464566886 +/- 0.0014856663200089155</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>0.011181102362204764 +/- 0.0009693535597175362</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.0034120734908136717 +/- 0.0007874015748031261</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.0011023622047244385 +/- 0.0007588888343727738</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-0.00031496062992124595 +/- 0.00041994750656165205</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>-0.00010498687664038942 +/- 0.0012153109609228502</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0.0036745406824147176 +/- 0.0009390311716534427</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>0.007716535433070893 +/- 0.0011023622047243921</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-5.249343832021136e-05 +/- 0.0001574803149606341</t>
+          <t>0.00041994750656169086 +/- 0.0008064195010885891</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.0004724409448818911 +/- 0.00028268581664746533</t>
+          <t>0.00041994750656169086 +/- 0.0005143285549151166</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.0001574803149606341 +/- 0.00047244094488190224</t>
+          <t>0.003832020997375352 +/- 0.0007442229332681008</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.0012598425196850061 +/- 0.0010809060515471793</t>
+          <t>0.005354330708661448 +/- 0.0008064195010885891</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0014698162729659182 +/- 0.00020997375328084543</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-0.0023622047244094 +/- 0.0009750223423100893</t>
+          <t>-0.0008398950131233262 +/- 0.00048111030918167975</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.004619422572178488 +/- 0.0008398950131233817</t>
+          <t>0.004461942257217888 +/- 0.0015616246488864532</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.007926509186351738 +/- 0.0013165287353264405</t>
+          <t>0.011128608923884554 +/- 0.0015712996899838068</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>5.249343832021136e-05 +/- 0.0001574803149606341</t>
+          <t>0.0010498687664042383 +/- 0.001197034567033228</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.017060367454068283 +/- 0.0014893712293030056</t>
+          <t>-0.006981627296587889 +/- 0.0014670014291319762</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.009921259842519726 +/- 0.0016838860821360036</t>
+          <t>-0.002467191601049845 +/- 0.0013290277061598055</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.0012598425196849727 +/- 0.0006299212598425141</t>
+          <t>0.0002624671916010568 +/- 0.0006321047022988249</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0021266540642721488 +/- 0.0007397200303638121</t>
+          <t>-0.0015122873345935427 +/- 0.001031069197980685</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,92 +4891,92 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.015879017013232466 +/- 0.0017707933832887635</t>
+          <t>-0.02660680529300562 +/- 0.002890534722754815</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.002788279773156843 +/- 0.0015011701487966736</t>
+          <t>-0.0005671077504725619 +/- 0.0008662713979122448</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.001035392358232828</t>
+          <t>0.003071833648393252 +/- 0.001357410833302947</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0009924385633270027 +/- 0.0013931382772196079</t>
+          <t>-0.0015122873345935206 +/- 0.001430316252402775</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.004678638941398905 +/- 0.0018719567410527718</t>
+          <t>0.000756143667296838 +/- 0.0023267549385805604</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.000567107750472573 +/- 0.0004630415392784812</t>
+          <t>0.00042533081285449635 +/- 0.00014177693761816543</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0030245746691872077 +/- 0.0013400233344761613</t>
+          <t>-0.0018903591682419175 +/- 0.0009685208663477812</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.01105860113421554 +/- 0.002982936453319365</t>
+          <t>0.0034026465028355935 +/- 0.002079395085066159</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.005812854442344107 +/- 0.002843797047888551</t>
+          <t>0.00326086956521745 +/- 0.004255670421494412</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.004017013232514221 +/- 0.0016675121705460518</t>
+          <t>0.011342155009451849 +/- 0.0012855832238880302</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.004584120982986817 +/- 0.0009224584733432324</t>
+          <t>-0.0005671077504725508 +/- 0.0009163856063168655</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.0034499054820415374 +/- 0.0014185568071648008</t>
+          <t>0.0004725897920605404 +/- 0.001768269086377101</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>-0.0020793950850661047 +/- 0.0021677400644952234</t>
+          <t>0.0047258979206049375 +/- 0.0031772658438509716</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.010586011342155066 +/- 0.0029603893692563043</t>
+          <t>-0.0022684310018903143 +/- 0.0020249797056359695</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0014650283553875542 +/- 0.0012223551187502575</t>
+          <t>0.0037807183364839793 +/- 0.0014334358117299745</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0017013232514177079 +/- 0.001706566170630215</t>
+          <t>-0.0025047258979205454 +/- 0.0009924385633270113</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.0029773156899810414 +/- 0.0008979206049149351</t>
+          <t>0.0016540642722117638 +/- 0.0006427916119440313</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.004111531190926243 +/- 0.0014185568071648001</t>
+          <t>-0.0028827977315689425 +/- 0.0013105316279642982</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4986,187 +4986,187 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.004158790170132387 +/- 0.0014146152691016831</t>
+          <t>-0.0013232514177693333 +/- 0.0016343682859915384</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.0014650283553874876 +/- 0.0012583673871166443</t>
+          <t>-0.006190926275992414 +/- 0.0014090785931829702</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0005671077504726396 +/- 0.001052507440988668</t>
+          <t>0.0017013232514178078 +/- 0.00070730763455083</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>0.004253308128544475 +/- 0.0008966760851138923</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.000850661625708915 +/- 0.0010735176457089535</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2.2204460492503132e-17 +/- 0.00029889202837130523</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-0.0028355387523628984 +/- 0.0018665801189160218</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-0.007136105860113384 +/- 0.0016967224074684699</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>-0.00023629489603020913 +/- 0.0011814744801512233</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.0009924385633270805 +/- 0.0011852491686185891</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.0003780718336484412 +/- 0.0001890359168242206</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.0007561436672968158 +/- 0.0003780718336483941</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.0020321361058601717 +/- 0.0007025552338052474</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-0.002315689981096369 +/- 0.0015879298314188377</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>0.00023629489603028687 +/- 0.0005283714502598674</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>0.0006616257088847277 +/- 0.000378071833648394</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>-0.0005198487712665068 +/- 0.0011073132810831578</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>0.0031190926275992846 +/- 0.0010609614518262665</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
           <t>-4.7258979206021844e-05 +/- 0.00033081285444234326</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-0.00014177693761812104 +/- 0.0007336566491616213</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0.0001890359168242206 +/- 0.00023152076963927118</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>-0.0036862003780718023 +/- 0.001398738051696491</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>0.0020793950850662157 +/- 0.0015844096988884965</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>-0.0030245746691870967 +/- 0.001482456251546125</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.0016540642722117527 +/- 0.0014373257396735107</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>9.451795841213251e-05 +/- 0.00035365381727542913</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.001370510396975455 +/- 0.0009320927657521846</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.0022684310018903143 +/- 0.0013987380516964723</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.002173913043478315 +/- 0.0010179895665660898</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-0.005387523629489577 +/- 0.001102259337399877</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.006663516068052977 +/- 0.0008828705903719063</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.0014177693761815101 +/- 0.0009212471025339373</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>-0.0011342155009451572 +/- 0.0013565879106244975</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
         <is>
           <t>0.00037807183364843013 +/- 0.0002835538752363087</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>9.451795841215471e-05 +/- 0.0014303162524027962</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-0.002599243856332656 +/- 0.001556679498298716</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>0.0005198487712665845 +/- 0.0002544973916415124</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>9.451795841215471e-05 +/- 0.0006269612080066978</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>-0.0013705103969753995 +/- 0.0009557537058675033</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>9.451795841214361e-05 +/- 0.0016614740861291921</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>0.0011342155009452237 +/- 0.0004331356989561545</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-4.7258979206010744e-05 +/- 0.00039256256441011874</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.00042533081285440756 +/- 0.001258367387116683</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>4.7258979206066255e-05 +/- 0.0007151581262013987</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-0.001039697542533058 +/- 0.001153738716042865</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0.0017013232514178078 +/- 0.0009731219414921686</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>-0.0008034026465028044 +/- 0.0007634921749245414</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>0.0002835538752363087 +/- 0.001180528922192518</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>-4.7258979206010744e-05 +/- 0.0005768693580214456</t>
-        </is>
-      </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.0002835538752362643 +/- 0.0008765234872869297</t>
+          <t>0.0024574669187146124 +/- 0.0008400939902945021</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.002315689981096458 +/- 0.0009078153455717866</t>
+          <t>0.0009924385633270695 +/- 0.000907815345571775</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.003071833648393263 +/- 0.0013408564233564413</t>
+          <t>0.0003308128544423861 +/- 0.001830942403384749</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.001275992438563367 +/- 0.0013705103969754411</t>
+          <t>0.007372400756143704 +/- 0.0011992984442769203</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>4.7258979206066255e-05 +/- 0.00025449739164152684</t>
+          <t>-0.0008506616257088706 +/- 0.0002835538752363087</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.0008506616257089372 +/- 0.000411994229068118</t>
+          <t>-9.4517958412077e-05 +/- 0.0005902644610962483</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0004725897920605515 +/- 0.0</t>
+          <t>0.0011342155009452127 +/- 0.00048194891432825823</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.005198487712665445 +/- 0.0013696953446303793</t>
+          <t>0.006001890359168283 +/- 0.0017046019656778196</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.005812854442344073 +/- 0.001449703369582039</t>
+          <t>0.011153119092627627 +/- 0.0010179895665660692</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,77 +5176,77 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0001890359168242206 +/- 0.00023152076963927118</t>
+          <t>-0.00023629489603023136 +/- 0.0004357062597964574</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.002599243856332756 +/- 0.000927288131869033</t>
+          <t>4.4408920985006264e-17 +/- 0.0007907939759301291</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.004584120982986828 +/- 0.0026401659212596253</t>
+          <t>-0.0014650283553874876 +/- 0.0012759924385633203</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.00037807183364843013 +/- 0.00041199422906811544</t>
+          <t>0.001275992438563367 +/- 0.0005996492221384672</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.001748582230623863 +/- 0.000670011667238083</t>
+          <t>-0.0004725897920604627 +/- 0.0008185495309871707</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0002835538752362754 +/- 0.0007382088540554578</t>
+          <t>0.004253308128544453 +/- 0.0016233992473835188</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-0.0008979206049149035 +/- 0.0010013998157096923</t>
+          <t>-0.00042533081285440756 +/- 0.0015306365539415612</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0009924385633270805 +/- 0.0007151581262014047</t>
+          <t>0.001843100189035951 +/- 0.0009320927657521874</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>-4.725897920604405e-05 +/- 0.00014177693761813215</t>
+          <t>9.45179584121103e-05 +/- 0.0001890359168242206</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.007183364839319517 +/- 0.001349986470423982</t>
+          <t>-0.00033081285444230835 +/- 0.0010787062580825358</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.0022211720226843366 +/- 0.0008467142186752886</t>
+          <t>0.001795841209829907 +/- 0.0009404418120100489</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.0015122873345936316 +/- 0.0006269612080067079</t>
+          <t>-0.0013232514177693333 +/- 0.0006616257088846707</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.0037807183364838683 +/- 0.001176739092437514</t>
+          <t>-0.0011814744801511789 +/- 0.0006766456079052793</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0011342155009451348 +/- 0.0013400233344761582</t>
+          <t>0.001843100189035951 +/- 0.0012583673871166745</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.00916824196597359 +/- 0.001180528922192535</t>
+          <t>0.005482041587901753 +/- 0.0012177787076299684</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.00037807183364843013 +/- 0.0002835538752363087</t>
+          <t>-0.00042533081285440756 +/- 0.0003925625644101294</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.0009451795841210142 +/- 0.0004226971602079162</t>
+          <t>0.0003780718336484412 +/- 0.000463041539278497</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>-0.0008506616257088595 +/- 0.0004630415392784813</t>
+          <t>0.0007088846880907828 +/- 0.00031702287015591545</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.0009924385633270695 +/- 0.0008572002432522396</t>
+          <t>0.003119092627599307 +/- 0.0012539224160133798</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0001890359168242206 +/- 0.0002315207696392712</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>4.725897920605515e-05 +/- 0.00014177693761816543</t>
+          <t>0.0003308128544423861 +/- 0.0013867108460416892</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.00316635160680534 +/- 0.0011776876932303552</t>
+          <t>-0.0027410207939508103 +/- 0.0011729370175794774</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.0032608695652174393 +/- 0.0008034026465028311</t>
+          <t>0.00023629489603027576 +/- 0.0007088846880907607</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0014650283553875542 +/- 0.0008828705903719017</t>
+          <t>0.0010396975425331246 +/- 0.00035365381727542913</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.0024574669187146015 +/- 0.0012104204607623586</t>
+          <t>0.0034026465028355823 +/- 0.0009163856063168826</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.0006616257088847167 +/- 0.0012177787076299562</t>
+          <t>0.0013705103969754774 +/- 0.0007751048897380538</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0006616257088847167 +/- 0.0006052102303812015</t>
+          <t>0.00023629489603027576 +/- 0.0005690734678068269</t>
         </is>
       </c>
     </row>
